--- a/docs/verification/M1_sim_vs_maxwell.xlsx
+++ b/docs/verification/M1_sim_vs_maxwell.xlsx
@@ -113,8 +113,8 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -563,12 +563,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'5b 시계열 데이터'!$A$2:$A$394</f>
+              <f>'5b 시계열 데이터'!$A$2:$A$399</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'5b 시계열 데이터'!$B$2:$B$394</f>
+              <f>'5b 시계열 데이터'!$B$2:$B$399</f>
             </numRef>
           </val>
         </ser>
@@ -595,12 +595,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'5b 시계열 데이터'!$A$2:$A$394</f>
+              <f>'5b 시계열 데이터'!$A$2:$A$399</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'5b 시계열 데이터'!$C$2:$C$394</f>
+              <f>'5b 시계열 데이터'!$C$2:$C$399</f>
             </numRef>
           </val>
         </ser>
@@ -627,12 +627,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'5b 시계열 데이터'!$A$2:$A$394</f>
+              <f>'5b 시계열 데이터'!$A$2:$A$399</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'5b 시계열 데이터'!$D$2:$D$394</f>
+              <f>'5b 시계열 데이터'!$D$2:$D$399</f>
             </numRef>
           </val>
         </ser>
@@ -659,12 +659,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'5b 시계열 데이터'!$A$2:$A$394</f>
+              <f>'5b 시계열 데이터'!$A$2:$A$399</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'5b 시계열 데이터'!$E$2:$E$394</f>
+              <f>'5b 시계열 데이터'!$E$2:$E$399</f>
             </numRef>
           </val>
         </ser>
@@ -1120,7 +1120,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>생성 2026-10-21 23:09:59 · 생성기 motor_dt_viz/tools/verify/sim_vs_maxwell_xlsx.py · 실행 커밋 46a2a96 · 새 해석·설정·엔진 변경 없음, 수기 숫자 없음</t>
+          <t>생성 2026-10-21 23:25:56 · 생성기 motor_dt_viz/tools/verify/sim_vs_maxwell_xlsx.py · 실행 커밋 2cd8914 · 새 해석·설정·엔진 변경 없음, 수기 숫자 없음</t>
         </is>
       </c>
     </row>
@@ -1216,10 +1216,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>556aa6c515e58169</t>
+          <t>8f1af0be7fa49d74</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>6c38a06cdc712700</t>
+          <t>b9adb4b8a2b4c7cc</t>
         </is>
       </c>
     </row>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>09b64411a0aa6eee</t>
+          <t>0c7524ce74150076</t>
         </is>
       </c>
     </row>
@@ -1558,7 +1558,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>5fcba17c82f6274d</t>
+          <t>8a73bc7b461565b9</t>
         </is>
       </c>
     </row>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ffaa16eb1b7b4e3c</t>
+          <t>be8476ed7628b493</t>
         </is>
       </c>
     </row>
@@ -2903,7 +2903,7 @@
         </is>
       </c>
       <c r="F23" s="4" t="n">
-        <v>2.99</v>
+        <v>2.98</v>
       </c>
       <c r="G23" s="5" t="n"/>
       <c r="H23" s="5" t="n">
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.05</v>
+        <v>2.95</v>
       </c>
       <c r="G34" s="5" t="n"/>
       <c r="H34" s="5" t="n">
@@ -3472,7 +3472,7 @@
       <c r="M34" t="n">
         <v>20</v>
       </c>
-      <c r="N34" s="10">
+      <c r="N34" s="6">
         <f>IF(ABS(K34)&lt;=M34,"PASS","FAIL")</f>
         <v/>
       </c>
@@ -4016,7 +4016,7 @@
         </is>
       </c>
       <c r="F45" s="4" t="n">
-        <v>2.96</v>
+        <v>3.03</v>
       </c>
       <c r="G45" s="5" t="n"/>
       <c r="H45" s="5" t="n">
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="F78" s="4" t="n">
-        <v>2.96</v>
+        <v>3.02</v>
       </c>
       <c r="G78" s="5" t="n"/>
       <c r="H78" s="5" t="n">
@@ -5759,7 +5759,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>556aa6c515e58169</t>
+          <t>8f1af0be7fa49d74</t>
         </is>
       </c>
     </row>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>6c38a06cdc712700</t>
+          <t>b9adb4b8a2b4c7cc</t>
         </is>
       </c>
     </row>
@@ -5912,7 +5912,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>09b64411a0aa6eee</t>
+          <t>0c7524ce74150076</t>
         </is>
       </c>
     </row>
@@ -5929,7 +5929,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>5fcba17c82f6274d</t>
+          <t>8a73bc7b461565b9</t>
         </is>
       </c>
     </row>
@@ -5946,7 +5946,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>ffaa16eb1b7b4e3c</t>
+          <t>be8476ed7628b493</t>
         </is>
       </c>
     </row>
@@ -6022,19 +6022,19 @@
           <t>정격 전류 I₁ [A]</t>
         </is>
       </c>
-      <c r="B2" s="11" t="n">
+      <c r="B2" s="10" t="n">
         <v>4.69464</v>
       </c>
-      <c r="C2" s="11" t="n">
+      <c r="C2" s="10" t="n">
         <v>4.73</v>
       </c>
-      <c r="D2" s="11" t="n">
+      <c r="D2" s="10" t="n">
         <v>4.67029</v>
       </c>
-      <c r="E2" s="11" t="n">
+      <c r="E2" s="10" t="n">
         <v>4.903921370548503</v>
       </c>
-      <c r="F2" s="11" t="n"/>
+      <c r="F2" s="10" t="n"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>허용차 없음(역률·효율로 간접)</t>
@@ -6052,19 +6052,19 @@
           <t>정상 r = I_R/I_n</t>
         </is>
       </c>
-      <c r="B3" s="11" t="n">
+      <c r="B3" s="10" t="n">
         <v>1.019323467230444</v>
       </c>
-      <c r="C3" s="11" t="n">
+      <c r="C3" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="D3" s="11" t="n">
+      <c r="D3" s="10" t="n">
         <v>0.9873763213530654</v>
       </c>
-      <c r="E3" s="11" t="n">
+      <c r="E3" s="10" t="n">
         <v>1.036769845781925</v>
       </c>
-      <c r="F3" s="11" t="n"/>
+      <c r="F3" s="10" t="n"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
@@ -6078,17 +6078,17 @@
           <t>역률</t>
         </is>
       </c>
-      <c r="B4" s="11" t="n"/>
-      <c r="C4" s="11" t="n">
+      <c r="B4" s="10" t="n"/>
+      <c r="C4" s="10" t="n">
         <v>0.79</v>
       </c>
-      <c r="D4" s="11" t="n">
+      <c r="D4" s="10" t="n">
         <v>0.790916</v>
       </c>
-      <c r="E4" s="11" t="n">
+      <c r="E4" s="10" t="n">
         <v>0.7400953642109238</v>
       </c>
-      <c r="F4" s="11" t="n"/>
+      <c r="F4" s="10" t="n"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>≥ 0.755</t>
@@ -6106,17 +6106,17 @@
           <t>효율</t>
         </is>
       </c>
-      <c r="B5" s="11" t="n"/>
-      <c r="C5" s="11" t="n">
+      <c r="B5" s="10" t="n"/>
+      <c r="C5" s="10" t="n">
         <v>0.895</v>
       </c>
-      <c r="D5" s="11" t="n">
+      <c r="D5" s="10" t="n">
         <v>0.895818</v>
       </c>
-      <c r="E5" s="11" t="n">
+      <c r="E5" s="10" t="n">
         <v>0.9146508966080783</v>
       </c>
-      <c r="F5" s="11" t="n"/>
+      <c r="F5" s="10" t="n"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>≥ 0.879</t>
@@ -6130,15 +6130,15 @@
           <t>정격 회전수 [rpm]</t>
         </is>
       </c>
-      <c r="B6" s="11" t="n"/>
-      <c r="C6" s="11" t="n">
+      <c r="B6" s="10" t="n"/>
+      <c r="C6" s="10" t="n">
         <v>1760</v>
       </c>
-      <c r="D6" s="11" t="n">
+      <c r="D6" s="10" t="n">
         <v>1755.1</v>
       </c>
-      <c r="E6" s="11" t="n"/>
-      <c r="F6" s="11" t="n"/>
+      <c r="E6" s="10" t="n"/>
+      <c r="F6" s="10" t="n"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>슬립 ±20 % → 0.0178~0.0266</t>
@@ -6152,17 +6152,17 @@
           <t>잠김 전류비 [×]</t>
         </is>
       </c>
-      <c r="B7" s="11" t="n"/>
-      <c r="C7" s="11" t="n">
+      <c r="B7" s="10" t="n"/>
+      <c r="C7" s="10" t="n">
         <v>6.5</v>
       </c>
-      <c r="D7" s="11" t="n">
+      <c r="D7" s="10" t="n">
         <v>8.240399999999999</v>
       </c>
-      <c r="E7" s="11" t="n">
+      <c r="E7" s="10" t="n">
         <v>8.247455775240095</v>
       </c>
-      <c r="F7" s="11" t="n">
+      <c r="F7" s="10" t="n">
         <v>7.429110695745793</v>
       </c>
       <c r="G7" t="inlineStr">
@@ -6182,17 +6182,17 @@
           <t>잠김 토크비 [×]</t>
         </is>
       </c>
-      <c r="B8" s="11" t="n"/>
-      <c r="C8" s="11" t="n">
+      <c r="B8" s="10" t="n"/>
+      <c r="C8" s="10" t="n">
         <v>2.1</v>
       </c>
-      <c r="D8" s="11" t="n">
+      <c r="D8" s="10" t="n">
         <v>3.08651</v>
       </c>
-      <c r="E8" s="11" t="n">
+      <c r="E8" s="10" t="n">
         <v>2.883091717080469</v>
       </c>
-      <c r="F8" s="11" t="n">
+      <c r="F8" s="10" t="n">
         <v>2.33933342694718</v>
       </c>
       <c r="G8" t="inlineStr">
@@ -6212,15 +6212,15 @@
           <t>최대 토크비 [×]</t>
         </is>
       </c>
-      <c r="B9" s="11" t="n"/>
-      <c r="C9" s="11" t="n">
+      <c r="B9" s="10" t="n"/>
+      <c r="C9" s="10" t="n">
         <v>2.5</v>
       </c>
-      <c r="D9" s="11" t="n">
+      <c r="D9" s="10" t="n">
         <v>4.15753</v>
       </c>
-      <c r="E9" s="11" t="n"/>
-      <c r="F9" s="11" t="n"/>
+      <c r="E9" s="10" t="n"/>
+      <c r="F9" s="10" t="n"/>
       <c r="G9" t="inlineStr">
         <is>
           <t>≥ 2.25</t>
@@ -6268,7 +6268,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>556aa6c515e58169</t>
+          <t>8f1af0be7fa49d74</t>
         </is>
       </c>
     </row>
@@ -6302,7 +6302,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>6c38a06cdc712700</t>
+          <t>b9adb4b8a2b4c7cc</t>
         </is>
       </c>
     </row>
@@ -6421,7 +6421,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>09b64411a0aa6eee</t>
+          <t>0c7524ce74150076</t>
         </is>
       </c>
     </row>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>5fcba17c82f6274d</t>
+          <t>8a73bc7b461565b9</t>
         </is>
       </c>
     </row>
@@ -6455,7 +6455,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ffaa16eb1b7b4e3c</t>
+          <t>be8476ed7628b493</t>
         </is>
       </c>
     </row>
@@ -7567,7 +7567,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>556aa6c515e58169</t>
+          <t>8f1af0be7fa49d74</t>
         </is>
       </c>
     </row>
@@ -7601,7 +7601,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>6c38a06cdc712700</t>
+          <t>b9adb4b8a2b4c7cc</t>
         </is>
       </c>
     </row>
@@ -7720,7 +7720,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>09b64411a0aa6eee</t>
+          <t>0c7524ce74150076</t>
         </is>
       </c>
     </row>
@@ -7737,7 +7737,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>5fcba17c82f6274d</t>
+          <t>8a73bc7b461565b9</t>
         </is>
       </c>
     </row>
@@ -7754,7 +7754,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ffaa16eb1b7b4e3c</t>
+          <t>be8476ed7628b493</t>
         </is>
       </c>
     </row>
@@ -8170,7 +8170,7 @@
           <t>DANGER</t>
         </is>
       </c>
-      <c r="J8" s="10" t="inlineStr">
+      <c r="J8" s="11" t="inlineStr">
         <is>
           <t>변화</t>
         </is>
@@ -8248,7 +8248,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>556aa6c515e58169</t>
+          <t>8f1af0be7fa49d74</t>
         </is>
       </c>
     </row>
@@ -8282,7 +8282,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>6c38a06cdc712700</t>
+          <t>b9adb4b8a2b4c7cc</t>
         </is>
       </c>
     </row>
@@ -8401,7 +8401,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>09b64411a0aa6eee</t>
+          <t>0c7524ce74150076</t>
         </is>
       </c>
     </row>
@@ -8418,7 +8418,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>5fcba17c82f6274d</t>
+          <t>8a73bc7b461565b9</t>
         </is>
       </c>
     </row>
@@ -8435,7 +8435,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ffaa16eb1b7b4e3c</t>
+          <t>be8476ed7628b493</t>
         </is>
       </c>
     </row>
@@ -8566,16 +8566,16 @@
         <v>20</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.04400000000000048</v>
+        <v>-0.02799999999999869</v>
       </c>
       <c r="F3" t="n">
-        <v>2.986000000000001</v>
+        <v>2.981999999999999</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.04400000000000048</v>
+        <v>-0.02799999999999869</v>
       </c>
       <c r="J3" t="n">
-        <v>2.986000000000001</v>
+        <v>2.981999999999999</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -8601,22 +8601,22 @@
         <v>165</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.05400000000000205</v>
+        <v>-0.02699999999998681</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.05400000000000205</v>
+        <v>-0.02699999999998681</v>
       </c>
       <c r="G4" t="n">
-        <v>2.959000000000003</v>
+        <v>3.006</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.05400000000000205</v>
+        <v>-0.02699999999998681</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.05400000000000205</v>
+        <v>-0.02699999999998681</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.05400000000000205</v>
+        <v>2.945999999999998</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -8642,25 +8642,25 @@
         <v>45</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.05400000000000205</v>
+        <v>-0.0140000000000029</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.05400000000000205</v>
+        <v>-0.0140000000000029</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.05400000000000205</v>
+        <v>-0.0140000000000029</v>
       </c>
       <c r="G5" t="n">
-        <v>2.959000000000003</v>
+        <v>3.029000000000003</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.05400000000000205</v>
+        <v>-0.0140000000000029</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.05400000000000205</v>
+        <v>-0.0140000000000029</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.05400000000000205</v>
+        <v>-0.0140000000000029</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -8686,22 +8686,22 @@
         <v>185</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.06200000000001182</v>
+        <v>-0.05500000000000682</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.06200000000001182</v>
+        <v>-0.05500000000000682</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.06200000000001182</v>
+        <v>-0.05500000000000682</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.06200000000001182</v>
+        <v>-0.05500000000000682</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.06200000000001182</v>
+        <v>-0.05500000000000682</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.06200000000001182</v>
+        <v>-0.05500000000000682</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -8750,13 +8750,13 @@
         <v>225</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.07699999999999818</v>
+        <v>-0.01499999999998636</v>
       </c>
       <c r="F8" t="n">
-        <v>2.961999999999989</v>
+        <v>3.018000000000001</v>
       </c>
       <c r="J8" t="n">
-        <v>2.961999999999989</v>
+        <v>3.018000000000001</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -8805,13 +8805,13 @@
         <v>20</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.03200000000000003</v>
+        <v>-0.08299999999999841</v>
       </c>
       <c r="F10" t="n">
-        <v>2.971</v>
+        <v>2.972000000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>2.971</v>
+        <v>2.972000000000001</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -8837,22 +8837,22 @@
         <v>165</v>
       </c>
       <c r="D11" t="n">
-        <v>0.01499999999998636</v>
+        <v>-0.08500000000000796</v>
       </c>
       <c r="E11" t="n">
-        <v>0.01499999999998636</v>
+        <v>-0.08500000000000796</v>
       </c>
       <c r="G11" t="n">
-        <v>3.050000000000011</v>
+        <v>2.938999999999993</v>
       </c>
       <c r="H11" t="n">
-        <v>0.01499999999998636</v>
+        <v>-0.08500000000000796</v>
       </c>
       <c r="I11" t="n">
-        <v>0.01499999999998636</v>
+        <v>-0.08500000000000796</v>
       </c>
       <c r="J11" t="n">
-        <v>0.01499999999998636</v>
+        <v>2.885999999999996</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -8878,25 +8878,25 @@
         <v>45</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.01299999999999812</v>
+        <v>-0.07999999999999829</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.01299999999999812</v>
+        <v>-0.07999999999999829</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.01299999999999812</v>
+        <v>-0.07999999999999829</v>
       </c>
       <c r="G12" t="n">
-        <v>3.003999999999998</v>
+        <v>2.942</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.01299999999999812</v>
+        <v>-0.07999999999999829</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.01299999999999812</v>
+        <v>-0.07999999999999829</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.01299999999999812</v>
+        <v>-0.07999999999999829</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -8922,22 +8922,22 @@
         <v>185</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.06100000000000705</v>
+        <v>-0.06299999999998818</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.06100000000000705</v>
+        <v>-0.06299999999998818</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.06100000000000705</v>
+        <v>-0.06299999999998818</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.06100000000000705</v>
+        <v>-0.06299999999998818</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.06100000000000705</v>
+        <v>-0.06299999999998818</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.06100000000000705</v>
+        <v>-0.06299999999998818</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -8986,13 +8986,13 @@
         <v>225</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.03600000000000136</v>
+        <v>-0.0589999999999975</v>
       </c>
       <c r="F15" t="n">
-        <v>2.973000000000013</v>
+        <v>2.974999999999994</v>
       </c>
       <c r="J15" t="n">
-        <v>2.973000000000013</v>
+        <v>2.974999999999994</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -9064,19 +9064,19 @@
         <v>165</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.04699999999999704</v>
+        <v>-0.06399999999999295</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.04699999999999704</v>
+        <v>-0.06399999999999295</v>
       </c>
       <c r="G18" t="n">
-        <v>2.991000000000014</v>
+        <v>2.98599999999999</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.04699999999999704</v>
+        <v>-0.06399999999999295</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.04699999999999704</v>
+        <v>2.98599999999999</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -9102,22 +9102,22 @@
         <v>45</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.02700000000000102</v>
+        <v>-0.06300000000000239</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.02700000000000102</v>
+        <v>-0.06300000000000239</v>
       </c>
       <c r="G19" t="n">
-        <v>2.979999999999997</v>
+        <v>2.939999999999998</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.02700000000000102</v>
+        <v>-0.06300000000000239</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.02700000000000102</v>
+        <v>-0.06300000000000239</v>
       </c>
       <c r="J19" t="n">
-        <v>2.979999999999997</v>
+        <v>2.939999999999998</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -9143,22 +9143,22 @@
         <v>185</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.04699999999999704</v>
+        <v>-0.02400000000000091</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.04699999999999704</v>
+        <v>-0.02400000000000091</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.04699999999999704</v>
+        <v>-0.02400000000000091</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.04699999999999704</v>
+        <v>-0.02400000000000091</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.04699999999999704</v>
+        <v>-0.02400000000000091</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.04699999999999704</v>
+        <v>-0.02400000000000091</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -9207,13 +9207,13 @@
         <v>225</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.07400000000001228</v>
+        <v>-0.04099999999999682</v>
       </c>
       <c r="F22" t="n">
-        <v>2.957999999999998</v>
+        <v>2.994</v>
       </c>
       <c r="J22" t="n">
-        <v>2.957999999999998</v>
+        <v>2.994</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -9278,7 +9278,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>556aa6c515e58169</t>
+          <t>8f1af0be7fa49d74</t>
         </is>
       </c>
     </row>
@@ -9312,7 +9312,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>6c38a06cdc712700</t>
+          <t>b9adb4b8a2b4c7cc</t>
         </is>
       </c>
     </row>
@@ -9431,7 +9431,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>09b64411a0aa6eee</t>
+          <t>0c7524ce74150076</t>
         </is>
       </c>
     </row>
@@ -9448,7 +9448,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>5fcba17c82f6274d</t>
+          <t>8a73bc7b461565b9</t>
         </is>
       </c>
     </row>
@@ -9465,7 +9465,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ffaa16eb1b7b4e3c</t>
+          <t>be8476ed7628b493</t>
         </is>
       </c>
     </row>
@@ -9481,7 +9481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E394"/>
+  <dimension ref="A1:E399"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9555,7 +9555,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>-19.62</v>
+        <v>-19.61</v>
       </c>
       <c r="B5" t="n">
         <v>0.027</v>
@@ -9569,7 +9569,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>-19.51</v>
+        <v>-19.49</v>
       </c>
       <c r="B6" t="n">
         <v>0.027</v>
@@ -9583,7 +9583,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>-19.4</v>
+        <v>-19.38</v>
       </c>
       <c r="B7" t="n">
         <v>0.027</v>
@@ -9597,7 +9597,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>-19.29</v>
+        <v>-19.27</v>
       </c>
       <c r="B8" t="n">
         <v>0.027</v>
@@ -9611,7 +9611,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>-19.18</v>
+        <v>-19.15</v>
       </c>
       <c r="B9" t="n">
         <v>0.027</v>
@@ -9625,7 +9625,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>-19.07</v>
+        <v>-19.04</v>
       </c>
       <c r="B10" t="n">
         <v>0.027</v>
@@ -9639,7 +9639,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>-18.96</v>
+        <v>-18.93</v>
       </c>
       <c r="B11" t="n">
         <v>0.027</v>
@@ -9653,7 +9653,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>-18.85</v>
+        <v>-18.82</v>
       </c>
       <c r="B12" t="n">
         <v>0.027</v>
@@ -9667,7 +9667,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>-18.73</v>
+        <v>-18.71</v>
       </c>
       <c r="B13" t="n">
         <v>0.027</v>
@@ -9681,7 +9681,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>-18.61</v>
+        <v>-18.59</v>
       </c>
       <c r="B14" t="n">
         <v>0.027</v>
@@ -9695,7 +9695,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>-18.5</v>
+        <v>-18.47</v>
       </c>
       <c r="B15" t="n">
         <v>0.027</v>
@@ -9709,7 +9709,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>-18.39</v>
+        <v>-18.37</v>
       </c>
       <c r="B16" t="n">
         <v>0.027</v>
@@ -9723,7 +9723,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>-18.28</v>
+        <v>-18.27</v>
       </c>
       <c r="B17" t="n">
         <v>0.027</v>
@@ -9737,7 +9737,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>-18.17</v>
+        <v>-18.16</v>
       </c>
       <c r="B18" t="n">
         <v>0.027</v>
@@ -9751,7 +9751,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>-18.03</v>
+        <v>-18.04</v>
       </c>
       <c r="B19" t="n">
         <v>0.027</v>
@@ -9765,7 +9765,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>-17.91</v>
+        <v>-17.93</v>
       </c>
       <c r="B20" t="n">
         <v>0.027</v>
@@ -9779,7 +9779,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>-17.8</v>
+        <v>-17.82</v>
       </c>
       <c r="B21" t="n">
         <v>0.027</v>
@@ -9807,7 +9807,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>-17.58</v>
+        <v>-17.59</v>
       </c>
       <c r="B23" t="n">
         <v>0.027</v>
@@ -9821,7 +9821,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>-17.46</v>
+        <v>-17.48</v>
       </c>
       <c r="B24" t="n">
         <v>0.027</v>
@@ -9835,7 +9835,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>-17.36</v>
+        <v>-17.37</v>
       </c>
       <c r="B25" t="n">
         <v>0.027</v>
@@ -9849,7 +9849,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>-17.25</v>
+        <v>-17.26</v>
       </c>
       <c r="B26" t="n">
         <v>0.027</v>
@@ -9863,7 +9863,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>-17.14</v>
+        <v>-17.15</v>
       </c>
       <c r="B27" t="n">
         <v>0.027</v>
@@ -9877,7 +9877,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>-17.03</v>
+        <v>-17.04</v>
       </c>
       <c r="B28" t="n">
         <v>0.027</v>
@@ -9891,7 +9891,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>-16.93</v>
+        <v>-16.92</v>
       </c>
       <c r="B29" t="n">
         <v>0.027</v>
@@ -9905,7 +9905,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>-16.82</v>
+        <v>-16.8</v>
       </c>
       <c r="B30" t="n">
         <v>0.027</v>
@@ -9919,7 +9919,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>-16.7</v>
+        <v>-16.69</v>
       </c>
       <c r="B31" t="n">
         <v>0.027</v>
@@ -9933,7 +9933,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>-16.59</v>
+        <v>-16.58</v>
       </c>
       <c r="B32" t="n">
         <v>0.027</v>
@@ -9947,7 +9947,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>-16.48</v>
+        <v>-16.47</v>
       </c>
       <c r="B33" t="n">
         <v>0.027</v>
@@ -9961,7 +9961,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>-16.38</v>
+        <v>-16.35</v>
       </c>
       <c r="B34" t="n">
         <v>0.027</v>
@@ -9975,7 +9975,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>-16.27</v>
+        <v>-16.24</v>
       </c>
       <c r="B35" t="n">
         <v>0.027</v>
@@ -9989,7 +9989,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>-16.16</v>
+        <v>-16.14</v>
       </c>
       <c r="B36" t="n">
         <v>0.027</v>
@@ -10003,7 +10003,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>-16.05</v>
+        <v>-16.03</v>
       </c>
       <c r="B37" t="n">
         <v>0.027</v>
@@ -10045,7 +10045,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>-15.66</v>
+        <v>-15.7</v>
       </c>
       <c r="B40" t="n">
         <v>0.027</v>
@@ -10059,7 +10059,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>-15.55</v>
+        <v>-15.59</v>
       </c>
       <c r="B41" t="n">
         <v>0.027</v>
@@ -10073,7 +10073,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>-15.44</v>
+        <v>-15.49</v>
       </c>
       <c r="B42" t="n">
         <v>0.027</v>
@@ -10087,7 +10087,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>-15.33</v>
+        <v>-15.38</v>
       </c>
       <c r="B43" t="n">
         <v>0.027</v>
@@ -10101,7 +10101,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>-15.21</v>
+        <v>-15.27</v>
       </c>
       <c r="B44" t="n">
         <v>0.027</v>
@@ -10115,7 +10115,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>-15.09</v>
+        <v>-15.16</v>
       </c>
       <c r="B45" t="n">
         <v>0.027</v>
@@ -10129,7 +10129,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>-14.99</v>
+        <v>-15.05</v>
       </c>
       <c r="B46" t="n">
         <v>0.027</v>
@@ -10143,7 +10143,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>-14.88</v>
+        <v>-14.95</v>
       </c>
       <c r="B47" t="n">
         <v>0.027</v>
@@ -10157,7 +10157,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>-14.76</v>
+        <v>-14.84</v>
       </c>
       <c r="B48" t="n">
         <v>0.027</v>
@@ -10171,7 +10171,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>-14.64</v>
+        <v>-14.73</v>
       </c>
       <c r="B49" t="n">
         <v>0.027</v>
@@ -10185,7 +10185,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>-14.53</v>
+        <v>-14.61</v>
       </c>
       <c r="B50" t="n">
         <v>0.027</v>
@@ -10199,7 +10199,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>-14.42</v>
+        <v>-14.5</v>
       </c>
       <c r="B51" t="n">
         <v>0.027</v>
@@ -10213,7 +10213,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>-14.31</v>
+        <v>-14.39</v>
       </c>
       <c r="B52" t="n">
         <v>0.027</v>
@@ -10227,7 +10227,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>-14.2</v>
+        <v>-14.28</v>
       </c>
       <c r="B53" t="n">
         <v>0.027</v>
@@ -10241,7 +10241,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>-14.08</v>
+        <v>-14.17</v>
       </c>
       <c r="B54" t="n">
         <v>0.027</v>
@@ -10255,7 +10255,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>-13.98</v>
+        <v>-14.04</v>
       </c>
       <c r="B55" t="n">
         <v>0.027</v>
@@ -10269,7 +10269,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>-13.87</v>
+        <v>-13.93</v>
       </c>
       <c r="B56" t="n">
         <v>0.027</v>
@@ -10283,7 +10283,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>-13.76</v>
+        <v>-13.81</v>
       </c>
       <c r="B57" t="n">
         <v>0.027</v>
@@ -10297,7 +10297,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>-13.65</v>
+        <v>-13.69</v>
       </c>
       <c r="B58" t="n">
         <v>0.027</v>
@@ -10311,7 +10311,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>-13.54</v>
+        <v>-13.59</v>
       </c>
       <c r="B59" t="n">
         <v>0.027</v>
@@ -10325,7 +10325,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>-13.43</v>
+        <v>-13.47</v>
       </c>
       <c r="B60" t="n">
         <v>0.027</v>
@@ -10339,7 +10339,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>-13.3</v>
+        <v>-13.34</v>
       </c>
       <c r="B61" t="n">
         <v>0.027</v>
@@ -10353,7 +10353,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>-13.18</v>
+        <v>-13.22</v>
       </c>
       <c r="B62" t="n">
         <v>0.027</v>
@@ -10367,7 +10367,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>-13.07</v>
+        <v>-13.12</v>
       </c>
       <c r="B63" t="n">
         <v>0.027</v>
@@ -10381,7 +10381,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>-12.96</v>
+        <v>-13.01</v>
       </c>
       <c r="B64" t="n">
         <v>0.027</v>
@@ -10395,7 +10395,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>-12.85</v>
+        <v>-12.91</v>
       </c>
       <c r="B65" t="n">
         <v>0.027</v>
@@ -10409,7 +10409,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>-12.75</v>
+        <v>-12.8</v>
       </c>
       <c r="B66" t="n">
         <v>0.027</v>
@@ -10423,7 +10423,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>-12.63</v>
+        <v>-12.67</v>
       </c>
       <c r="B67" t="n">
         <v>0.027</v>
@@ -10437,7 +10437,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>-12.52</v>
+        <v>-12.56</v>
       </c>
       <c r="B68" t="n">
         <v>0.027</v>
@@ -10451,7 +10451,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>-12.4</v>
+        <v>-12.46</v>
       </c>
       <c r="B69" t="n">
         <v>0.027</v>
@@ -10465,7 +10465,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>-12.28</v>
+        <v>-12.34</v>
       </c>
       <c r="B70" t="n">
         <v>0.027</v>
@@ -10479,7 +10479,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>-12.18</v>
+        <v>-12.23</v>
       </c>
       <c r="B71" t="n">
         <v>0.027</v>
@@ -10493,7 +10493,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>-12.07</v>
+        <v>-12.13</v>
       </c>
       <c r="B72" t="n">
         <v>0.027</v>
@@ -10507,7 +10507,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>-11.9</v>
+        <v>-12.02</v>
       </c>
       <c r="B73" t="n">
         <v>0.027</v>
@@ -10521,7 +10521,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>-11.8</v>
+        <v>-11.86</v>
       </c>
       <c r="B74" t="n">
         <v>0.027</v>
@@ -10535,7 +10535,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>-11.69</v>
+        <v>-11.75</v>
       </c>
       <c r="B75" t="n">
         <v>0.027</v>
@@ -10549,7 +10549,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>-11.57</v>
+        <v>-11.63</v>
       </c>
       <c r="B76" t="n">
         <v>0.027</v>
@@ -10563,7 +10563,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>-11.46</v>
+        <v>-11.53</v>
       </c>
       <c r="B77" t="n">
         <v>0.027</v>
@@ -10577,7 +10577,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>-11.35</v>
+        <v>-11.42</v>
       </c>
       <c r="B78" t="n">
         <v>0.027</v>
@@ -10591,7 +10591,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>-11.25</v>
+        <v>-11.3</v>
       </c>
       <c r="B79" t="n">
         <v>0.027</v>
@@ -10605,7 +10605,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>-11.14</v>
+        <v>-11.18</v>
       </c>
       <c r="B80" t="n">
         <v>0.027</v>
@@ -10619,7 +10619,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>-11.02</v>
+        <v>-11.08</v>
       </c>
       <c r="B81" t="n">
         <v>0.027</v>
@@ -10633,7 +10633,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>-10.91</v>
+        <v>-10.97</v>
       </c>
       <c r="B82" t="n">
         <v>0.027</v>
@@ -10647,7 +10647,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>-10.81</v>
+        <v>-10.87</v>
       </c>
       <c r="B83" t="n">
         <v>0.027</v>
@@ -10661,7 +10661,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>-10.69</v>
+        <v>-10.75</v>
       </c>
       <c r="B84" t="n">
         <v>0.027</v>
@@ -10675,7 +10675,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>-10.58</v>
+        <v>-10.63</v>
       </c>
       <c r="B85" t="n">
         <v>0.027</v>
@@ -10689,7 +10689,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>-10.47</v>
+        <v>-10.53</v>
       </c>
       <c r="B86" t="n">
         <v>0.027</v>
@@ -10703,7 +10703,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>-10.36</v>
+        <v>-10.42</v>
       </c>
       <c r="B87" t="n">
         <v>0.027</v>
@@ -10717,7 +10717,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>-10.25</v>
+        <v>-10.31</v>
       </c>
       <c r="B88" t="n">
         <v>0.027</v>
@@ -10731,7 +10731,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>-10.14</v>
+        <v>-10.2</v>
       </c>
       <c r="B89" t="n">
         <v>0.027</v>
@@ -10745,7 +10745,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>-10.03</v>
+        <v>-10.08</v>
       </c>
       <c r="B90" t="n">
         <v>0.027</v>
@@ -10759,7 +10759,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>-9.93</v>
+        <v>-9.960000000000001</v>
       </c>
       <c r="B91" t="n">
         <v>0.027</v>
@@ -10773,7 +10773,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>-9.81</v>
+        <v>-9.85</v>
       </c>
       <c r="B92" t="n">
         <v>0.027</v>
@@ -10787,7 +10787,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>-9.710000000000001</v>
+        <v>-9.75</v>
       </c>
       <c r="B93" t="n">
         <v>0.027</v>
@@ -10801,7 +10801,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>-9.58</v>
+        <v>-9.630000000000001</v>
       </c>
       <c r="B94" t="n">
         <v>0.027</v>
@@ -10815,7 +10815,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>-9.470000000000001</v>
+        <v>-9.52</v>
       </c>
       <c r="B95" t="n">
         <v>0.027</v>
@@ -10829,7 +10829,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>-9.369999999999999</v>
+        <v>-9.4</v>
       </c>
       <c r="B96" t="n">
         <v>0.027</v>
@@ -10843,7 +10843,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>-9.25</v>
+        <v>-9.289999999999999</v>
       </c>
       <c r="B97" t="n">
         <v>0.027</v>
@@ -10857,7 +10857,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>-9.130000000000001</v>
+        <v>-9.19</v>
       </c>
       <c r="B98" t="n">
         <v>0.027</v>
@@ -10871,7 +10871,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>-9.029999999999999</v>
+        <v>-9.07</v>
       </c>
       <c r="B99" t="n">
         <v>0.027</v>
@@ -10885,7 +10885,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>-8.92</v>
+        <v>-8.970000000000001</v>
       </c>
       <c r="B100" t="n">
         <v>0.027</v>
@@ -10899,7 +10899,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>-8.800000000000001</v>
+        <v>-8.859999999999999</v>
       </c>
       <c r="B101" t="n">
         <v>0.027</v>
@@ -10913,7 +10913,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>-8.699999999999999</v>
+        <v>-8.75</v>
       </c>
       <c r="B102" t="n">
         <v>0.027</v>
@@ -10927,7 +10927,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>-8.59</v>
+        <v>-8.65</v>
       </c>
       <c r="B103" t="n">
         <v>0.027</v>
@@ -10941,7 +10941,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>-8.470000000000001</v>
+        <v>-8.539999999999999</v>
       </c>
       <c r="B104" t="n">
         <v>0.027</v>
@@ -10955,7 +10955,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>-8.369999999999999</v>
+        <v>-8.43</v>
       </c>
       <c r="B105" t="n">
         <v>0.027</v>
@@ -10969,7 +10969,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>-8.26</v>
+        <v>-8.289999999999999</v>
       </c>
       <c r="B106" t="n">
         <v>0.027</v>
@@ -10983,7 +10983,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>-8.16</v>
+        <v>-8.17</v>
       </c>
       <c r="B107" t="n">
         <v>0.027</v>
@@ -10997,7 +10997,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>-8.039999999999999</v>
+        <v>-8.01</v>
       </c>
       <c r="B108" t="n">
         <v>0.027</v>
@@ -11011,7 +11011,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>-7.92</v>
+        <v>-7.91</v>
       </c>
       <c r="B109" t="n">
         <v>0.027</v>
@@ -11025,7 +11025,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>-7.8</v>
+        <v>-7.78</v>
       </c>
       <c r="B110" t="n">
         <v>0.027</v>
@@ -11039,7 +11039,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>-7.69</v>
+        <v>-7.67</v>
       </c>
       <c r="B111" t="n">
         <v>0.027</v>
@@ -11053,7 +11053,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>-7.56</v>
+        <v>-7.54</v>
       </c>
       <c r="B112" t="n">
         <v>0.027</v>
@@ -11067,7 +11067,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>-7.45</v>
+        <v>-7.42</v>
       </c>
       <c r="B113" t="n">
         <v>0.027</v>
@@ -11081,7 +11081,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>-7.34</v>
+        <v>-7.31</v>
       </c>
       <c r="B114" t="n">
         <v>0.027</v>
@@ -11095,7 +11095,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>-7.24</v>
+        <v>-7.19</v>
       </c>
       <c r="B115" t="n">
         <v>0.027</v>
@@ -11109,7 +11109,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>-7.12</v>
+        <v>-7.08</v>
       </c>
       <c r="B116" t="n">
         <v>0.027</v>
@@ -11123,7 +11123,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>-7.01</v>
+        <v>-6.96</v>
       </c>
       <c r="B117" t="n">
         <v>0.027</v>
@@ -11137,7 +11137,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>-6.89</v>
+        <v>-6.85</v>
       </c>
       <c r="B118" t="n">
         <v>0.027</v>
@@ -11151,7 +11151,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>-6.78</v>
+        <v>-6.74</v>
       </c>
       <c r="B119" t="n">
         <v>0.027</v>
@@ -11165,7 +11165,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>-6.67</v>
+        <v>-6.62</v>
       </c>
       <c r="B120" t="n">
         <v>0.027</v>
@@ -11179,7 +11179,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>-6.55</v>
+        <v>-6.51</v>
       </c>
       <c r="B121" t="n">
         <v>0.027</v>
@@ -11193,7 +11193,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>-6.43</v>
+        <v>-6.39</v>
       </c>
       <c r="B122" t="n">
         <v>0.027</v>
@@ -11207,7 +11207,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>-6.32</v>
+        <v>-6.29</v>
       </c>
       <c r="B123" t="n">
         <v>0.027</v>
@@ -11221,7 +11221,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>-6.21</v>
+        <v>-6.16</v>
       </c>
       <c r="B124" t="n">
         <v>0.027</v>
@@ -11235,7 +11235,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>-6.09</v>
+        <v>-6.04</v>
       </c>
       <c r="B125" t="n">
         <v>0.027</v>
@@ -11249,7 +11249,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>-5.98</v>
+        <v>-5.93</v>
       </c>
       <c r="B126" t="n">
         <v>0.027</v>
@@ -11263,7 +11263,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>-5.87</v>
+        <v>-5.82</v>
       </c>
       <c r="B127" t="n">
         <v>0.027</v>
@@ -11277,7 +11277,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>-5.74</v>
+        <v>-5.71</v>
       </c>
       <c r="B128" t="n">
         <v>0.027</v>
@@ -11291,7 +11291,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>-5.63</v>
+        <v>-5.59</v>
       </c>
       <c r="B129" t="n">
         <v>0.027</v>
@@ -11305,7 +11305,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>-5.51</v>
+        <v>-5.48</v>
       </c>
       <c r="B130" t="n">
         <v>0.027</v>
@@ -11319,7 +11319,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>-5.4</v>
+        <v>-5.37</v>
       </c>
       <c r="B131" t="n">
         <v>0.027</v>
@@ -11333,7 +11333,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>-5.28</v>
+        <v>-5.25</v>
       </c>
       <c r="B132" t="n">
         <v>0.027</v>
@@ -11347,7 +11347,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>-5.16</v>
+        <v>-5.14</v>
       </c>
       <c r="B133" t="n">
         <v>0.027</v>
@@ -11361,7 +11361,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>-5.05</v>
+        <v>-5.03</v>
       </c>
       <c r="B134" t="n">
         <v>0.027</v>
@@ -11375,7 +11375,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>-4.94</v>
+        <v>-4.92</v>
       </c>
       <c r="B135" t="n">
         <v>0.027</v>
@@ -11389,7 +11389,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>-4.83</v>
+        <v>-4.8</v>
       </c>
       <c r="B136" t="n">
         <v>0.027</v>
@@ -11403,7 +11403,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>-4.71</v>
+        <v>-4.69</v>
       </c>
       <c r="B137" t="n">
         <v>0.027</v>
@@ -11417,7 +11417,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>-4.6</v>
+        <v>-4.57</v>
       </c>
       <c r="B138" t="n">
         <v>0.027</v>
@@ -11431,7 +11431,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>-4.48</v>
+        <v>-4.46</v>
       </c>
       <c r="B139" t="n">
         <v>0.027</v>
@@ -11445,7 +11445,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>-4.37</v>
+        <v>-4.35</v>
       </c>
       <c r="B140" t="n">
         <v>0.027</v>
@@ -11473,7 +11473,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>-4.13</v>
+        <v>-4.1</v>
       </c>
       <c r="B142" t="n">
         <v>0.027</v>
@@ -11487,7 +11487,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>-4.01</v>
+        <v>-3.99</v>
       </c>
       <c r="B143" t="n">
         <v>0.027</v>
@@ -11501,7 +11501,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>-3.9</v>
+        <v>-3.88</v>
       </c>
       <c r="B144" t="n">
         <v>0.027</v>
@@ -11515,7 +11515,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>-3.79</v>
+        <v>-3.78</v>
       </c>
       <c r="B145" t="n">
         <v>0.027</v>
@@ -11529,7 +11529,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>-3.67</v>
+        <v>-3.66</v>
       </c>
       <c r="B146" t="n">
         <v>0.027</v>
@@ -11557,7 +11557,7 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>-3.44</v>
+        <v>-3.45</v>
       </c>
       <c r="B148" t="n">
         <v>0.027</v>
@@ -11571,7 +11571,7 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>-3.32</v>
+        <v>-3.34</v>
       </c>
       <c r="B149" t="n">
         <v>0.027</v>
@@ -11585,7 +11585,7 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>-3.21</v>
+        <v>-3.23</v>
       </c>
       <c r="B150" t="n">
         <v>0.027</v>
@@ -11599,7 +11599,7 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>-3.1</v>
+        <v>-3.11</v>
       </c>
       <c r="B151" t="n">
         <v>0.027</v>
@@ -11613,7 +11613,7 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>-2.98</v>
+        <v>-3.01</v>
       </c>
       <c r="B152" t="n">
         <v>0.027</v>
@@ -11627,7 +11627,7 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>-2.86</v>
+        <v>-2.89</v>
       </c>
       <c r="B153" t="n">
         <v>0.027</v>
@@ -11641,7 +11641,7 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>-2.75</v>
+        <v>-2.79</v>
       </c>
       <c r="B154" t="n">
         <v>0.027</v>
@@ -11655,7 +11655,7 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>-2.63</v>
+        <v>-2.68</v>
       </c>
       <c r="B155" t="n">
         <v>0.027</v>
@@ -11669,7 +11669,7 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>-2.52</v>
+        <v>-2.56</v>
       </c>
       <c r="B156" t="n">
         <v>0.027</v>
@@ -11683,7 +11683,7 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>-2.41</v>
+        <v>-2.46</v>
       </c>
       <c r="B157" t="n">
         <v>0.027</v>
@@ -11697,7 +11697,7 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>-2.29</v>
+        <v>-2.35</v>
       </c>
       <c r="B158" t="n">
         <v>0.027</v>
@@ -11711,7 +11711,7 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>-2.18</v>
+        <v>-2.23</v>
       </c>
       <c r="B159" t="n">
         <v>0.027</v>
@@ -11725,7 +11725,7 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>-2.06</v>
+        <v>-2.13</v>
       </c>
       <c r="B160" t="n">
         <v>0.027</v>
@@ -11739,7 +11739,7 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>-1.94</v>
+        <v>-2</v>
       </c>
       <c r="B161" t="n">
         <v>0.027</v>
@@ -11753,7 +11753,7 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>-1.82</v>
+        <v>-1.89</v>
       </c>
       <c r="B162" t="n">
         <v>0.027</v>
@@ -11767,7 +11767,7 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>-1.71</v>
+        <v>-1.77</v>
       </c>
       <c r="B163" t="n">
         <v>0.027</v>
@@ -11781,7 +11781,7 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>-1.57</v>
+        <v>-1.66</v>
       </c>
       <c r="B164" t="n">
         <v>0.027</v>
@@ -11795,7 +11795,7 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>-1.46</v>
+        <v>-1.56</v>
       </c>
       <c r="B165" t="n">
         <v>0.027</v>
@@ -11809,7 +11809,7 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>-1.35</v>
+        <v>-1.44</v>
       </c>
       <c r="B166" t="n">
         <v>0.027</v>
@@ -11823,7 +11823,7 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>-1.24</v>
+        <v>-1.33</v>
       </c>
       <c r="B167" t="n">
         <v>0.027</v>
@@ -11837,7 +11837,7 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>-1.13</v>
+        <v>-1.23</v>
       </c>
       <c r="B168" t="n">
         <v>0.027</v>
@@ -11851,7 +11851,7 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>-1.02</v>
+        <v>-1.11</v>
       </c>
       <c r="B169" t="n">
         <v>0.027</v>
@@ -11865,7 +11865,7 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>-0.91</v>
+        <v>-0.99</v>
       </c>
       <c r="B170" t="n">
         <v>0.027</v>
@@ -11879,7 +11879,7 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>-0.8</v>
+        <v>-0.87</v>
       </c>
       <c r="B171" t="n">
         <v>0.027</v>
@@ -11893,7 +11893,7 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>-0.68</v>
+        <v>-0.76</v>
       </c>
       <c r="B172" t="n">
         <v>0.027</v>
@@ -11907,7 +11907,7 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.65</v>
       </c>
       <c r="B173" t="n">
         <v>0.027</v>
@@ -11921,7 +11921,7 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>-0.45</v>
+        <v>-0.54</v>
       </c>
       <c r="B174" t="n">
         <v>0.027</v>
@@ -11935,7 +11935,7 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>-0.32</v>
+        <v>-0.43</v>
       </c>
       <c r="B175" t="n">
         <v>0.027</v>
@@ -11949,7 +11949,7 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>-0.21</v>
+        <v>-0.32</v>
       </c>
       <c r="B176" t="n">
         <v>0.027</v>
@@ -11963,7 +11963,7 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>-0.1</v>
+        <v>-0.21</v>
       </c>
       <c r="B177" t="n">
         <v>0.027</v>
@@ -11977,10 +11977,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>0.01</v>
+        <v>-0.09</v>
       </c>
       <c r="B178" t="n">
-        <v>0.07262</v>
+        <v>0.027</v>
       </c>
       <c r="D178" t="n">
         <v>0.05</v>
@@ -11991,7 +11991,7 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>0.12</v>
+        <v>0.03</v>
       </c>
       <c r="B179" t="n">
         <v>0.07262</v>
@@ -12005,7 +12005,7 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>0.25</v>
+        <v>0.14</v>
       </c>
       <c r="B180" t="n">
         <v>0.07262</v>
@@ -12019,7 +12019,7 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>0.37</v>
+        <v>0.26</v>
       </c>
       <c r="B181" t="n">
         <v>0.07262</v>
@@ -12033,7 +12033,7 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>0.49</v>
+        <v>0.37</v>
       </c>
       <c r="B182" t="n">
         <v>0.07262</v>
@@ -12047,7 +12047,7 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>0.6</v>
+        <v>0.48</v>
       </c>
       <c r="B183" t="n">
         <v>0.07262</v>
@@ -12061,10 +12061,13 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>0.72</v>
+        <v>0.6</v>
       </c>
       <c r="B184" t="n">
         <v>0.07262</v>
+      </c>
+      <c r="C184" t="n">
+        <v>0.26958</v>
       </c>
       <c r="D184" t="n">
         <v>0.05</v>
@@ -12075,10 +12078,13 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>0.82</v>
+        <v>0.72</v>
       </c>
       <c r="B185" t="n">
         <v>0.07262</v>
+      </c>
+      <c r="C185" t="n">
+        <v>0.26958</v>
       </c>
       <c r="D185" t="n">
         <v>0.05</v>
@@ -12089,7 +12095,7 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>0.93</v>
+        <v>0.84</v>
       </c>
       <c r="B186" t="n">
         <v>0.07262</v>
@@ -12103,13 +12109,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>1.04</v>
+        <v>0.97</v>
       </c>
       <c r="B187" t="n">
         <v>0.07262</v>
-      </c>
-      <c r="C187" t="n">
-        <v>0.26958</v>
       </c>
       <c r="D187" t="n">
         <v>0.05</v>
@@ -12120,13 +12123,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="B188" t="n">
         <v>0.07262</v>
-      </c>
-      <c r="C188" t="n">
-        <v>0.26958</v>
       </c>
       <c r="D188" t="n">
         <v>0.05</v>
@@ -12137,7 +12137,7 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="B189" t="n">
         <v>0.07262</v>
@@ -12151,7 +12151,7 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="B190" t="n">
         <v>0.07262</v>
@@ -12165,7 +12165,7 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="B191" t="n">
         <v>0.07262</v>
@@ -12179,7 +12179,7 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="B192" t="n">
         <v>0.07262</v>
@@ -12193,13 +12193,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="B193" t="n">
         <v>0.07262</v>
-      </c>
-      <c r="C193" t="n">
-        <v>0.26958</v>
       </c>
       <c r="D193" t="n">
         <v>0.05</v>
@@ -12210,7 +12207,7 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="B194" t="n">
         <v>0.07262</v>
@@ -12224,7 +12221,7 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="B195" t="n">
         <v>0.07262</v>
@@ -12238,7 +12235,7 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="B196" t="n">
         <v>0.07262</v>
@@ -12252,13 +12249,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="B197" t="n">
         <v>0.07262</v>
-      </c>
-      <c r="C197" t="n">
-        <v>0.26958</v>
       </c>
       <c r="D197" t="n">
         <v>0.05</v>
@@ -12269,7 +12263,7 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="B198" t="n">
         <v>0.07262</v>
@@ -12283,13 +12277,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="B199" t="n">
         <v>0.07262</v>
-      </c>
-      <c r="C199" t="n">
-        <v>0.26958</v>
       </c>
       <c r="D199" t="n">
         <v>0.05</v>
@@ -12300,7 +12291,7 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>2.49</v>
+        <v>2.44</v>
       </c>
       <c r="B200" t="n">
         <v>0.07262</v>
@@ -12314,7 +12305,7 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>2.61</v>
+        <v>2.55</v>
       </c>
       <c r="B201" t="n">
         <v>0.07262</v>
@@ -12328,7 +12319,7 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>2.71</v>
+        <v>2.66</v>
       </c>
       <c r="B202" t="n">
         <v>0.07262</v>
@@ -12342,7 +12333,7 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>2.82</v>
+        <v>2.77</v>
       </c>
       <c r="B203" t="n">
         <v>0.07262</v>
@@ -12356,7 +12347,7 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>2.94</v>
+        <v>2.87</v>
       </c>
       <c r="B204" t="n">
         <v>0.07262</v>
@@ -12370,7 +12361,7 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>3.06</v>
+        <v>2.98</v>
       </c>
       <c r="B205" t="n">
         <v>0.07262</v>
@@ -12384,10 +12375,13 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>3.17</v>
+        <v>3.09</v>
       </c>
       <c r="B206" t="n">
         <v>0.07262</v>
+      </c>
+      <c r="C206" t="n">
+        <v>0.26958</v>
       </c>
       <c r="D206" t="n">
         <v>0.05</v>
@@ -12398,13 +12392,10 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>3.28</v>
+        <v>3.21</v>
       </c>
       <c r="B207" t="n">
         <v>0.07262</v>
-      </c>
-      <c r="C207" t="n">
-        <v>0.26958</v>
       </c>
       <c r="D207" t="n">
         <v>0.05</v>
@@ -12415,7 +12406,7 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>3.39</v>
+        <v>3.32</v>
       </c>
       <c r="B208" t="n">
         <v>0.07262</v>
@@ -12429,7 +12420,7 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>3.5</v>
+        <v>3.43</v>
       </c>
       <c r="B209" t="n">
         <v>0.07262</v>
@@ -12443,13 +12434,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>3.62</v>
+        <v>3.53</v>
       </c>
       <c r="B210" t="n">
         <v>0.07262</v>
-      </c>
-      <c r="C210" t="n">
-        <v>0.26958</v>
       </c>
       <c r="D210" t="n">
         <v>0.05</v>
@@ -12460,13 +12448,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>3.73</v>
+        <v>3.65</v>
       </c>
       <c r="B211" t="n">
         <v>0.07262</v>
-      </c>
-      <c r="C211" t="n">
-        <v>0.26958</v>
       </c>
       <c r="D211" t="n">
         <v>0.05</v>
@@ -12477,7 +12462,7 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>3.84</v>
+        <v>3.77</v>
       </c>
       <c r="B212" t="n">
         <v>0.07262</v>
@@ -12494,7 +12479,7 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>3.95</v>
+        <v>3.89</v>
       </c>
       <c r="B213" t="n">
         <v>0.07262</v>
@@ -12508,10 +12493,13 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>4.06</v>
+        <v>4</v>
       </c>
       <c r="B214" t="n">
         <v>0.07262</v>
+      </c>
+      <c r="C214" t="n">
+        <v>0.26958</v>
       </c>
       <c r="D214" t="n">
         <v>0.05</v>
@@ -12522,13 +12510,10 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>4.18</v>
+        <v>4.12</v>
       </c>
       <c r="B215" t="n">
         <v>0.07262</v>
-      </c>
-      <c r="C215" t="n">
-        <v>0.26958</v>
       </c>
       <c r="D215" t="n">
         <v>0.05</v>
@@ -12539,13 +12524,10 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>4.29</v>
+        <v>4.23</v>
       </c>
       <c r="B216" t="n">
         <v>0.07262</v>
-      </c>
-      <c r="C216" t="n">
-        <v>0.26958</v>
       </c>
       <c r="D216" t="n">
         <v>0.05</v>
@@ -12556,13 +12538,10 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>4.41</v>
+        <v>4.34</v>
       </c>
       <c r="B217" t="n">
         <v>0.07262</v>
-      </c>
-      <c r="C217" t="n">
-        <v>0.26958</v>
       </c>
       <c r="D217" t="n">
         <v>0.05</v>
@@ -12573,13 +12552,10 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>4.52</v>
+        <v>4.45</v>
       </c>
       <c r="B218" t="n">
         <v>0.07262</v>
-      </c>
-      <c r="C218" t="n">
-        <v>0.26958</v>
       </c>
       <c r="D218" t="n">
         <v>0.05</v>
@@ -12590,10 +12566,13 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>4.65</v>
+        <v>4.55</v>
       </c>
       <c r="B219" t="n">
         <v>0.07262</v>
+      </c>
+      <c r="C219" t="n">
+        <v>0.26958</v>
       </c>
       <c r="D219" t="n">
         <v>0.05</v>
@@ -12604,7 +12583,7 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>4.77</v>
+        <v>4.67</v>
       </c>
       <c r="B220" t="n">
         <v>0.07262</v>
@@ -12618,7 +12597,7 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>4.88</v>
+        <v>4.79</v>
       </c>
       <c r="B221" t="n">
         <v>0.07262</v>
@@ -12632,7 +12611,7 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>5</v>
+        <v>4.89</v>
       </c>
       <c r="B222" t="n">
         <v>0.07262</v>
@@ -12646,7 +12625,7 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>5.12</v>
+        <v>5.01</v>
       </c>
       <c r="B223" t="n">
         <v>0.07262</v>
@@ -12660,10 +12639,13 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>5.23</v>
+        <v>5.11</v>
       </c>
       <c r="B224" t="n">
         <v>0.07262</v>
+      </c>
+      <c r="C224" t="n">
+        <v>0.26958</v>
       </c>
       <c r="D224" t="n">
         <v>0.05</v>
@@ -12674,10 +12656,13 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>5.34</v>
+        <v>5.23</v>
       </c>
       <c r="B225" t="n">
         <v>0.07262</v>
+      </c>
+      <c r="C225" t="n">
+        <v>0.26958</v>
       </c>
       <c r="D225" t="n">
         <v>0.05</v>
@@ -12688,7 +12673,7 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>5.46</v>
+        <v>5.34</v>
       </c>
       <c r="B226" t="n">
         <v>0.07262</v>
@@ -12702,7 +12687,7 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>5.57</v>
+        <v>5.45</v>
       </c>
       <c r="B227" t="n">
         <v>0.07262</v>
@@ -12716,7 +12701,7 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>5.68</v>
+        <v>5.56</v>
       </c>
       <c r="B228" t="n">
         <v>0.07262</v>
@@ -12730,13 +12715,10 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>5.8</v>
+        <v>5.68</v>
       </c>
       <c r="B229" t="n">
         <v>0.07262</v>
-      </c>
-      <c r="C229" t="n">
-        <v>0.26958</v>
       </c>
       <c r="D229" t="n">
         <v>0.05</v>
@@ -12747,7 +12729,7 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>5.92</v>
+        <v>5.78</v>
       </c>
       <c r="B230" t="n">
         <v>0.07262</v>
@@ -12761,7 +12743,7 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>6.03</v>
+        <v>5.9</v>
       </c>
       <c r="B231" t="n">
         <v>0.07262</v>
@@ -12775,7 +12757,7 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>6.14</v>
+        <v>6.01</v>
       </c>
       <c r="B232" t="n">
         <v>0.07262</v>
@@ -12789,7 +12771,7 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>6.25</v>
+        <v>6.12</v>
       </c>
       <c r="B233" t="n">
         <v>0.07262</v>
@@ -12803,7 +12785,7 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>6.37</v>
+        <v>6.23</v>
       </c>
       <c r="B234" t="n">
         <v>0.07262</v>
@@ -12817,7 +12799,7 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>6.48</v>
+        <v>6.35</v>
       </c>
       <c r="B235" t="n">
         <v>0.07262</v>
@@ -12831,7 +12813,7 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>6.6</v>
+        <v>6.47</v>
       </c>
       <c r="B236" t="n">
         <v>0.07262</v>
@@ -12845,7 +12827,7 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>6.71</v>
+        <v>6.57</v>
       </c>
       <c r="B237" t="n">
         <v>0.07262</v>
@@ -12859,7 +12841,7 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>6.82</v>
+        <v>6.68</v>
       </c>
       <c r="B238" t="n">
         <v>0.07262</v>
@@ -12873,7 +12855,7 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>6.94</v>
+        <v>6.79</v>
       </c>
       <c r="B239" t="n">
         <v>0.07262</v>
@@ -12887,13 +12869,10 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>7.05</v>
+        <v>6.91</v>
       </c>
       <c r="B240" t="n">
         <v>0.07262</v>
-      </c>
-      <c r="C240" t="n">
-        <v>0.26958</v>
       </c>
       <c r="D240" t="n">
         <v>0.05</v>
@@ -12904,10 +12883,13 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>7.17</v>
+        <v>7.01</v>
       </c>
       <c r="B241" t="n">
         <v>0.07262</v>
+      </c>
+      <c r="C241" t="n">
+        <v>0.26958</v>
       </c>
       <c r="D241" t="n">
         <v>0.05</v>
@@ -12918,10 +12900,13 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>7.28</v>
+        <v>7.12</v>
       </c>
       <c r="B242" t="n">
         <v>0.07262</v>
+      </c>
+      <c r="C242" t="n">
+        <v>0.26958</v>
       </c>
       <c r="D242" t="n">
         <v>0.05</v>
@@ -12932,10 +12917,13 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>7.39</v>
+        <v>7.23</v>
       </c>
       <c r="B243" t="n">
         <v>0.07262</v>
+      </c>
+      <c r="C243" t="n">
+        <v>0.26958</v>
       </c>
       <c r="D243" t="n">
         <v>0.05</v>
@@ -12946,7 +12934,7 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>7.52</v>
+        <v>7.36</v>
       </c>
       <c r="B244" t="n">
         <v>0.07262</v>
@@ -12960,7 +12948,7 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>7.62</v>
+        <v>7.46</v>
       </c>
       <c r="B245" t="n">
         <v>0.07262</v>
@@ -12974,7 +12962,7 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>7.74</v>
+        <v>7.56</v>
       </c>
       <c r="B246" t="n">
         <v>0.07262</v>
@@ -12991,7 +12979,7 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>7.84</v>
+        <v>7.67</v>
       </c>
       <c r="B247" t="n">
         <v>0.07262</v>
@@ -13005,13 +12993,10 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>7.96</v>
+        <v>7.78</v>
       </c>
       <c r="B248" t="n">
         <v>0.07262</v>
-      </c>
-      <c r="C248" t="n">
-        <v>0.26958</v>
       </c>
       <c r="D248" t="n">
         <v>0.05</v>
@@ -13022,13 +13007,10 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>8.07</v>
+        <v>7.9</v>
       </c>
       <c r="B249" t="n">
         <v>0.07262</v>
-      </c>
-      <c r="C249" t="n">
-        <v>0.26958</v>
       </c>
       <c r="D249" t="n">
         <v>0.05</v>
@@ -13039,7 +13021,7 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>8.18</v>
+        <v>8</v>
       </c>
       <c r="B250" t="n">
         <v>0.07262</v>
@@ -13053,7 +13035,7 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>8.300000000000001</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="B251" t="n">
         <v>0.07262</v>
@@ -13067,7 +13049,7 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>8.42</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="B252" t="n">
         <v>0.07262</v>
@@ -13081,10 +13063,13 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>8.539999999999999</v>
+        <v>8.32</v>
       </c>
       <c r="B253" t="n">
         <v>0.07262</v>
+      </c>
+      <c r="C253" t="n">
+        <v>0.26958</v>
       </c>
       <c r="D253" t="n">
         <v>0.05</v>
@@ -13095,10 +13080,13 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>8.640000000000001</v>
+        <v>8.43</v>
       </c>
       <c r="B254" t="n">
         <v>0.07262</v>
+      </c>
+      <c r="C254" t="n">
+        <v>0.26958</v>
       </c>
       <c r="D254" t="n">
         <v>0.05</v>
@@ -13109,10 +13097,13 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>8.76</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="B255" t="n">
         <v>0.07262</v>
+      </c>
+      <c r="C255" t="n">
+        <v>0.26958</v>
       </c>
       <c r="D255" t="n">
         <v>0.05</v>
@@ -13123,7 +13114,7 @@
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>8.880000000000001</v>
+        <v>8.65</v>
       </c>
       <c r="B256" t="n">
         <v>0.07262</v>
@@ -13137,10 +13128,13 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>9</v>
+        <v>8.77</v>
       </c>
       <c r="B257" t="n">
         <v>0.07262</v>
+      </c>
+      <c r="C257" t="n">
+        <v>0.26958</v>
       </c>
       <c r="D257" t="n">
         <v>0.05</v>
@@ -13151,7 +13145,7 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>9.119999999999999</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="B258" t="n">
         <v>0.07262</v>
@@ -13165,13 +13159,10 @@
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>9.24</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="B259" t="n">
         <v>0.07262</v>
-      </c>
-      <c r="C259" t="n">
-        <v>0.26958</v>
       </c>
       <c r="D259" t="n">
         <v>0.05</v>
@@ -13182,7 +13173,7 @@
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>9.34</v>
+        <v>9.15</v>
       </c>
       <c r="B260" t="n">
         <v>0.07262</v>
@@ -13196,10 +13187,13 @@
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>9.449999999999999</v>
+        <v>9.27</v>
       </c>
       <c r="B261" t="n">
         <v>0.07262</v>
+      </c>
+      <c r="C261" t="n">
+        <v>0.26958</v>
       </c>
       <c r="D261" t="n">
         <v>0.05</v>
@@ -13210,10 +13204,13 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>9.56</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="B262" t="n">
         <v>0.07262</v>
+      </c>
+      <c r="C262" t="n">
+        <v>0.26958</v>
       </c>
       <c r="D262" t="n">
         <v>0.05</v>
@@ -13224,10 +13221,13 @@
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>9.68</v>
+        <v>9.48</v>
       </c>
       <c r="B263" t="n">
         <v>0.07262</v>
+      </c>
+      <c r="C263" t="n">
+        <v>0.26958</v>
       </c>
       <c r="D263" t="n">
         <v>0.05</v>
@@ -13238,13 +13238,10 @@
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>9.789999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="B264" t="n">
         <v>0.07262</v>
-      </c>
-      <c r="C264" t="n">
-        <v>0.26958</v>
       </c>
       <c r="D264" t="n">
         <v>0.05</v>
@@ -13255,13 +13252,10 @@
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>9.9</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="B265" t="n">
         <v>0.07262</v>
-      </c>
-      <c r="C265" t="n">
-        <v>0.26958</v>
       </c>
       <c r="D265" t="n">
         <v>0.05</v>
@@ -13272,7 +13266,7 @@
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>10.02</v>
+        <v>9.82</v>
       </c>
       <c r="B266" t="n">
         <v>0.07262</v>
@@ -13286,13 +13280,10 @@
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>10.12</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="B267" t="n">
         <v>0.07262</v>
-      </c>
-      <c r="C267" t="n">
-        <v>0.26958</v>
       </c>
       <c r="D267" t="n">
         <v>0.05</v>
@@ -13303,13 +13294,10 @@
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>10.24</v>
+        <v>10.09</v>
       </c>
       <c r="B268" t="n">
         <v>0.07262</v>
-      </c>
-      <c r="C268" t="n">
-        <v>0.26958</v>
       </c>
       <c r="D268" t="n">
         <v>0.05</v>
@@ -13320,13 +13308,10 @@
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>10.35</v>
+        <v>10.21</v>
       </c>
       <c r="B269" t="n">
         <v>0.07262</v>
-      </c>
-      <c r="C269" t="n">
-        <v>0.26958</v>
       </c>
       <c r="D269" t="n">
         <v>0.05</v>
@@ -13337,7 +13322,7 @@
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>10.45</v>
+        <v>10.32</v>
       </c>
       <c r="B270" t="n">
         <v>0.07262</v>
@@ -13351,7 +13336,7 @@
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>10.57</v>
+        <v>10.44</v>
       </c>
       <c r="B271" t="n">
         <v>0.07262</v>
@@ -13365,7 +13350,7 @@
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>10.69</v>
+        <v>10.55</v>
       </c>
       <c r="B272" t="n">
         <v>0.07262</v>
@@ -13379,10 +13364,13 @@
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>10.8</v>
+        <v>10.67</v>
       </c>
       <c r="B273" t="n">
         <v>0.07262</v>
+      </c>
+      <c r="C273" t="n">
+        <v>0.26958</v>
       </c>
       <c r="D273" t="n">
         <v>0.05</v>
@@ -13393,10 +13381,13 @@
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>10.92</v>
+        <v>10.78</v>
       </c>
       <c r="B274" t="n">
         <v>0.07262</v>
+      </c>
+      <c r="C274" t="n">
+        <v>0.26958</v>
       </c>
       <c r="D274" t="n">
         <v>0.05</v>
@@ -13407,7 +13398,7 @@
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>11.03</v>
+        <v>10.89</v>
       </c>
       <c r="B275" t="n">
         <v>0.07262</v>
@@ -13421,10 +13412,13 @@
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>11.15</v>
+        <v>11.02</v>
       </c>
       <c r="B276" t="n">
         <v>0.07262</v>
+      </c>
+      <c r="C276" t="n">
+        <v>0.26958</v>
       </c>
       <c r="D276" t="n">
         <v>0.05</v>
@@ -13435,7 +13429,7 @@
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>11.27</v>
+        <v>11.12</v>
       </c>
       <c r="B277" t="n">
         <v>0.07262</v>
@@ -13449,10 +13443,13 @@
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>11.38</v>
+        <v>11.24</v>
       </c>
       <c r="B278" t="n">
         <v>0.07262</v>
+      </c>
+      <c r="C278" t="n">
+        <v>0.26958</v>
       </c>
       <c r="D278" t="n">
         <v>0.05</v>
@@ -13463,7 +13460,7 @@
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>11.49</v>
+        <v>11.35</v>
       </c>
       <c r="B279" t="n">
         <v>0.07262</v>
@@ -13477,10 +13474,13 @@
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>11.61</v>
+        <v>11.46</v>
       </c>
       <c r="B280" t="n">
         <v>0.07262</v>
+      </c>
+      <c r="C280" t="n">
+        <v>0.26958</v>
       </c>
       <c r="D280" t="n">
         <v>0.05</v>
@@ -13491,7 +13491,7 @@
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>11.73</v>
+        <v>11.56</v>
       </c>
       <c r="B281" t="n">
         <v>0.07262</v>
@@ -13505,13 +13505,10 @@
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>11.85</v>
+        <v>11.67</v>
       </c>
       <c r="B282" t="n">
         <v>0.07262</v>
-      </c>
-      <c r="C282" t="n">
-        <v>0.26958</v>
       </c>
       <c r="D282" t="n">
         <v>0.05</v>
@@ -13522,13 +13519,10 @@
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>11.97</v>
+        <v>11.79</v>
       </c>
       <c r="B283" t="n">
         <v>0.07262</v>
-      </c>
-      <c r="C283" t="n">
-        <v>0.26958</v>
       </c>
       <c r="D283" t="n">
         <v>0.05</v>
@@ -13539,7 +13533,7 @@
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>12.09</v>
+        <v>11.89</v>
       </c>
       <c r="B284" t="n">
         <v>0.07262</v>
@@ -13553,7 +13547,7 @@
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>12.22</v>
+        <v>11.99</v>
       </c>
       <c r="B285" t="n">
         <v>0.07262</v>
@@ -13567,7 +13561,7 @@
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>12.34</v>
+        <v>12.09</v>
       </c>
       <c r="B286" t="n">
         <v>0.07262</v>
@@ -13581,7 +13575,7 @@
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>12.45</v>
+        <v>12.21</v>
       </c>
       <c r="B287" t="n">
         <v>0.07262</v>
@@ -13595,7 +13589,7 @@
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>12.57</v>
+        <v>12.31</v>
       </c>
       <c r="B288" t="n">
         <v>0.07262</v>
@@ -13609,7 +13603,7 @@
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>12.68</v>
+        <v>12.42</v>
       </c>
       <c r="B289" t="n">
         <v>0.07262</v>
@@ -13623,7 +13617,7 @@
     </row>
     <row r="290">
       <c r="A290" t="n">
-        <v>12.79</v>
+        <v>12.54</v>
       </c>
       <c r="B290" t="n">
         <v>0.07262</v>
@@ -13637,7 +13631,7 @@
     </row>
     <row r="291">
       <c r="A291" t="n">
-        <v>12.9</v>
+        <v>12.64</v>
       </c>
       <c r="B291" t="n">
         <v>0.07262</v>
@@ -13651,10 +13645,13 @@
     </row>
     <row r="292">
       <c r="A292" t="n">
-        <v>13</v>
+        <v>12.75</v>
       </c>
       <c r="B292" t="n">
         <v>0.07262</v>
+      </c>
+      <c r="C292" t="n">
+        <v>0.26958</v>
       </c>
       <c r="D292" t="n">
         <v>0.05</v>
@@ -13665,10 +13662,13 @@
     </row>
     <row r="293">
       <c r="A293" t="n">
-        <v>13.11</v>
+        <v>12.85</v>
       </c>
       <c r="B293" t="n">
         <v>0.07262</v>
+      </c>
+      <c r="C293" t="n">
+        <v>0.26958</v>
       </c>
       <c r="D293" t="n">
         <v>0.05</v>
@@ -13679,7 +13679,7 @@
     </row>
     <row r="294">
       <c r="A294" t="n">
-        <v>13.23</v>
+        <v>12.98</v>
       </c>
       <c r="B294" t="n">
         <v>0.07262</v>
@@ -13693,7 +13693,7 @@
     </row>
     <row r="295">
       <c r="A295" t="n">
-        <v>13.34</v>
+        <v>13.09</v>
       </c>
       <c r="B295" t="n">
         <v>0.07262</v>
@@ -13707,13 +13707,10 @@
     </row>
     <row r="296">
       <c r="A296" t="n">
-        <v>13.46</v>
+        <v>13.21</v>
       </c>
       <c r="B296" t="n">
         <v>0.07262</v>
-      </c>
-      <c r="C296" t="n">
-        <v>0.26958</v>
       </c>
       <c r="D296" t="n">
         <v>0.05</v>
@@ -13724,7 +13721,7 @@
     </row>
     <row r="297">
       <c r="A297" t="n">
-        <v>13.57</v>
+        <v>13.32</v>
       </c>
       <c r="B297" t="n">
         <v>0.07262</v>
@@ -13738,7 +13735,7 @@
     </row>
     <row r="298">
       <c r="A298" t="n">
-        <v>13.68</v>
+        <v>13.43</v>
       </c>
       <c r="B298" t="n">
         <v>0.07262</v>
@@ -13752,7 +13749,7 @@
     </row>
     <row r="299">
       <c r="A299" t="n">
-        <v>13.82</v>
+        <v>13.56</v>
       </c>
       <c r="B299" t="n">
         <v>0.07262</v>
@@ -13766,10 +13763,13 @@
     </row>
     <row r="300">
       <c r="A300" t="n">
-        <v>13.93</v>
+        <v>13.67</v>
       </c>
       <c r="B300" t="n">
         <v>0.07262</v>
+      </c>
+      <c r="C300" t="n">
+        <v>0.26958</v>
       </c>
       <c r="D300" t="n">
         <v>0.05</v>
@@ -13780,7 +13780,7 @@
     </row>
     <row r="301">
       <c r="A301" t="n">
-        <v>14.04</v>
+        <v>13.79</v>
       </c>
       <c r="B301" t="n">
         <v>0.07262</v>
@@ -13794,10 +13794,13 @@
     </row>
     <row r="302">
       <c r="A302" t="n">
-        <v>14.15</v>
+        <v>13.89</v>
       </c>
       <c r="B302" t="n">
         <v>0.07262</v>
+      </c>
+      <c r="C302" t="n">
+        <v>0.26958</v>
       </c>
       <c r="D302" t="n">
         <v>0.05</v>
@@ -13808,7 +13811,7 @@
     </row>
     <row r="303">
       <c r="A303" t="n">
-        <v>14.27</v>
+        <v>14.01</v>
       </c>
       <c r="B303" t="n">
         <v>0.07262</v>
@@ -13825,10 +13828,13 @@
     </row>
     <row r="304">
       <c r="A304" t="n">
-        <v>14.38</v>
+        <v>14.12</v>
       </c>
       <c r="B304" t="n">
         <v>0.07262</v>
+      </c>
+      <c r="C304" t="n">
+        <v>0.26958</v>
       </c>
       <c r="D304" t="n">
         <v>0.05</v>
@@ -13839,10 +13845,13 @@
     </row>
     <row r="305">
       <c r="A305" t="n">
-        <v>14.49</v>
+        <v>14.23</v>
       </c>
       <c r="B305" t="n">
         <v>0.07262</v>
+      </c>
+      <c r="C305" t="n">
+        <v>0.26958</v>
       </c>
       <c r="D305" t="n">
         <v>0.05</v>
@@ -13853,7 +13862,7 @@
     </row>
     <row r="306">
       <c r="A306" t="n">
-        <v>14.62</v>
+        <v>14.34</v>
       </c>
       <c r="B306" t="n">
         <v>0.07262</v>
@@ -13867,10 +13876,13 @@
     </row>
     <row r="307">
       <c r="A307" t="n">
-        <v>14.73</v>
+        <v>14.45</v>
       </c>
       <c r="B307" t="n">
         <v>0.07262</v>
+      </c>
+      <c r="C307" t="n">
+        <v>0.26958</v>
       </c>
       <c r="D307" t="n">
         <v>0.05</v>
@@ -13881,10 +13893,13 @@
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>14.86</v>
+        <v>14.56</v>
       </c>
       <c r="B308" t="n">
         <v>0.07262</v>
+      </c>
+      <c r="C308" t="n">
+        <v>0.26958</v>
       </c>
       <c r="D308" t="n">
         <v>0.05</v>
@@ -13895,7 +13910,7 @@
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>14.98</v>
+        <v>14.68</v>
       </c>
       <c r="B309" t="n">
         <v>0.07262</v>
@@ -13909,7 +13924,7 @@
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>15.09</v>
+        <v>14.8</v>
       </c>
       <c r="B310" t="n">
         <v>0.07262</v>
@@ -13923,7 +13938,7 @@
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>15.21</v>
+        <v>14.91</v>
       </c>
       <c r="B311" t="n">
         <v>0.07262</v>
@@ -13937,7 +13952,7 @@
     </row>
     <row r="312">
       <c r="A312" t="n">
-        <v>15.33</v>
+        <v>15.03</v>
       </c>
       <c r="B312" t="n">
         <v>0.07262</v>
@@ -13951,7 +13966,7 @@
     </row>
     <row r="313">
       <c r="A313" t="n">
-        <v>15.44</v>
+        <v>15.14</v>
       </c>
       <c r="B313" t="n">
         <v>0.07262</v>
@@ -13965,10 +13980,13 @@
     </row>
     <row r="314">
       <c r="A314" t="n">
-        <v>15.55</v>
+        <v>15.25</v>
       </c>
       <c r="B314" t="n">
         <v>0.07262</v>
+      </c>
+      <c r="C314" t="n">
+        <v>0.26958</v>
       </c>
       <c r="D314" t="n">
         <v>0.05</v>
@@ -13979,13 +13997,10 @@
     </row>
     <row r="315">
       <c r="A315" t="n">
-        <v>15.67</v>
+        <v>15.36</v>
       </c>
       <c r="B315" t="n">
         <v>0.07262</v>
-      </c>
-      <c r="C315" t="n">
-        <v>0.26958</v>
       </c>
       <c r="D315" t="n">
         <v>0.05</v>
@@ -13996,7 +14011,7 @@
     </row>
     <row r="316">
       <c r="A316" t="n">
-        <v>15.79</v>
+        <v>15.48</v>
       </c>
       <c r="B316" t="n">
         <v>0.07262</v>
@@ -14010,7 +14025,7 @@
     </row>
     <row r="317">
       <c r="A317" t="n">
-        <v>15.91</v>
+        <v>15.59</v>
       </c>
       <c r="B317" t="n">
         <v>0.07262</v>
@@ -14024,10 +14039,13 @@
     </row>
     <row r="318">
       <c r="A318" t="n">
-        <v>16.01</v>
+        <v>15.7</v>
       </c>
       <c r="B318" t="n">
         <v>0.07262</v>
+      </c>
+      <c r="C318" t="n">
+        <v>0.26958</v>
       </c>
       <c r="D318" t="n">
         <v>0.05</v>
@@ -14038,7 +14056,7 @@
     </row>
     <row r="319">
       <c r="A319" t="n">
-        <v>16.12</v>
+        <v>15.81</v>
       </c>
       <c r="B319" t="n">
         <v>0.07262</v>
@@ -14052,7 +14070,7 @@
     </row>
     <row r="320">
       <c r="A320" t="n">
-        <v>16.23</v>
+        <v>15.92</v>
       </c>
       <c r="B320" t="n">
         <v>0.07262</v>
@@ -14066,7 +14084,7 @@
     </row>
     <row r="321">
       <c r="A321" t="n">
-        <v>16.34</v>
+        <v>16.03</v>
       </c>
       <c r="B321" t="n">
         <v>0.07262</v>
@@ -14080,10 +14098,13 @@
     </row>
     <row r="322">
       <c r="A322" t="n">
-        <v>16.44</v>
+        <v>16.15</v>
       </c>
       <c r="B322" t="n">
         <v>0.07262</v>
+      </c>
+      <c r="C322" t="n">
+        <v>0.26958</v>
       </c>
       <c r="D322" t="n">
         <v>0.05</v>
@@ -14094,7 +14115,7 @@
     </row>
     <row r="323">
       <c r="A323" t="n">
-        <v>16.56</v>
+        <v>16.26</v>
       </c>
       <c r="B323" t="n">
         <v>0.07262</v>
@@ -14108,7 +14129,7 @@
     </row>
     <row r="324">
       <c r="A324" t="n">
-        <v>16.68</v>
+        <v>16.38</v>
       </c>
       <c r="B324" t="n">
         <v>0.07262</v>
@@ -14122,10 +14143,13 @@
     </row>
     <row r="325">
       <c r="A325" t="n">
-        <v>16.79</v>
+        <v>16.5</v>
       </c>
       <c r="B325" t="n">
         <v>0.07262</v>
+      </c>
+      <c r="C325" t="n">
+        <v>0.26958</v>
       </c>
       <c r="D325" t="n">
         <v>0.05</v>
@@ -14136,7 +14160,7 @@
     </row>
     <row r="326">
       <c r="A326" t="n">
-        <v>16.9</v>
+        <v>16.63</v>
       </c>
       <c r="B326" t="n">
         <v>0.07262</v>
@@ -14150,7 +14174,7 @@
     </row>
     <row r="327">
       <c r="A327" t="n">
-        <v>17.01</v>
+        <v>16.75</v>
       </c>
       <c r="B327" t="n">
         <v>0.07262</v>
@@ -14164,7 +14188,7 @@
     </row>
     <row r="328">
       <c r="A328" t="n">
-        <v>17.12</v>
+        <v>16.87</v>
       </c>
       <c r="B328" t="n">
         <v>0.07262</v>
@@ -14178,13 +14202,10 @@
     </row>
     <row r="329">
       <c r="A329" t="n">
-        <v>17.24</v>
+        <v>16.99</v>
       </c>
       <c r="B329" t="n">
         <v>0.07262</v>
-      </c>
-      <c r="C329" t="n">
-        <v>0.26958</v>
       </c>
       <c r="D329" t="n">
         <v>0.05</v>
@@ -14195,7 +14216,7 @@
     </row>
     <row r="330">
       <c r="A330" t="n">
-        <v>17.36</v>
+        <v>17.09</v>
       </c>
       <c r="B330" t="n">
         <v>0.07262</v>
@@ -14209,7 +14230,7 @@
     </row>
     <row r="331">
       <c r="A331" t="n">
-        <v>17.5</v>
+        <v>17.2</v>
       </c>
       <c r="B331" t="n">
         <v>0.07262</v>
@@ -14223,13 +14244,10 @@
     </row>
     <row r="332">
       <c r="A332" t="n">
-        <v>17.62</v>
+        <v>17.31</v>
       </c>
       <c r="B332" t="n">
         <v>0.07262</v>
-      </c>
-      <c r="C332" t="n">
-        <v>0.26958</v>
       </c>
       <c r="D332" t="n">
         <v>0.05</v>
@@ -14240,7 +14258,7 @@
     </row>
     <row r="333">
       <c r="A333" t="n">
-        <v>17.73</v>
+        <v>17.43</v>
       </c>
       <c r="B333" t="n">
         <v>0.07262</v>
@@ -14254,7 +14272,7 @@
     </row>
     <row r="334">
       <c r="A334" t="n">
-        <v>17.85</v>
+        <v>17.53</v>
       </c>
       <c r="B334" t="n">
         <v>0.07262</v>
@@ -14268,7 +14286,7 @@
     </row>
     <row r="335">
       <c r="A335" t="n">
-        <v>17.96</v>
+        <v>17.64</v>
       </c>
       <c r="B335" t="n">
         <v>0.07262</v>
@@ -14282,13 +14300,10 @@
     </row>
     <row r="336">
       <c r="A336" t="n">
-        <v>18.08</v>
+        <v>17.76</v>
       </c>
       <c r="B336" t="n">
         <v>0.07262</v>
-      </c>
-      <c r="C336" t="n">
-        <v>0.26958</v>
       </c>
       <c r="D336" t="n">
         <v>0.05</v>
@@ -14299,7 +14314,7 @@
     </row>
     <row r="337">
       <c r="A337" t="n">
-        <v>18.2</v>
+        <v>17.87</v>
       </c>
       <c r="B337" t="n">
         <v>0.07262</v>
@@ -14313,13 +14328,10 @@
     </row>
     <row r="338">
       <c r="A338" t="n">
-        <v>18.31</v>
+        <v>17.99</v>
       </c>
       <c r="B338" t="n">
         <v>0.07262</v>
-      </c>
-      <c r="C338" t="n">
-        <v>0.26958</v>
       </c>
       <c r="D338" t="n">
         <v>0.05</v>
@@ -14330,7 +14342,7 @@
     </row>
     <row r="339">
       <c r="A339" t="n">
-        <v>18.43</v>
+        <v>18.11</v>
       </c>
       <c r="B339" t="n">
         <v>0.07262</v>
@@ -14344,7 +14356,7 @@
     </row>
     <row r="340">
       <c r="A340" t="n">
-        <v>18.54</v>
+        <v>18.22</v>
       </c>
       <c r="B340" t="n">
         <v>0.07262</v>
@@ -14358,7 +14370,7 @@
     </row>
     <row r="341">
       <c r="A341" t="n">
-        <v>18.69</v>
+        <v>18.34</v>
       </c>
       <c r="B341" t="n">
         <v>0.07262</v>
@@ -14372,7 +14384,7 @@
     </row>
     <row r="342">
       <c r="A342" t="n">
-        <v>18.8</v>
+        <v>18.47</v>
       </c>
       <c r="B342" t="n">
         <v>0.07262</v>
@@ -14386,7 +14398,7 @@
     </row>
     <row r="343">
       <c r="A343" t="n">
-        <v>18.92</v>
+        <v>18.58</v>
       </c>
       <c r="B343" t="n">
         <v>0.07262</v>
@@ -14403,13 +14415,10 @@
     </row>
     <row r="344">
       <c r="A344" t="n">
-        <v>19.04</v>
+        <v>18.69</v>
       </c>
       <c r="B344" t="n">
         <v>0.07262</v>
-      </c>
-      <c r="C344" t="n">
-        <v>0.26958</v>
       </c>
       <c r="D344" t="n">
         <v>0.05</v>
@@ -14420,13 +14429,10 @@
     </row>
     <row r="345">
       <c r="A345" t="n">
-        <v>19.15</v>
+        <v>18.81</v>
       </c>
       <c r="B345" t="n">
         <v>0.07262</v>
-      </c>
-      <c r="C345" t="n">
-        <v>0.26958</v>
       </c>
       <c r="D345" t="n">
         <v>0.05</v>
@@ -14437,13 +14443,10 @@
     </row>
     <row r="346">
       <c r="A346" t="n">
-        <v>19.26</v>
+        <v>18.91</v>
       </c>
       <c r="B346" t="n">
         <v>0.07262</v>
-      </c>
-      <c r="C346" t="n">
-        <v>0.26958</v>
       </c>
       <c r="D346" t="n">
         <v>0.05</v>
@@ -14454,7 +14457,7 @@
     </row>
     <row r="347">
       <c r="A347" t="n">
-        <v>19.36</v>
+        <v>19.02</v>
       </c>
       <c r="B347" t="n">
         <v>0.07262</v>
@@ -14468,7 +14471,7 @@
     </row>
     <row r="348">
       <c r="A348" t="n">
-        <v>19.48</v>
+        <v>19.13</v>
       </c>
       <c r="B348" t="n">
         <v>0.07262</v>
@@ -14482,13 +14485,10 @@
     </row>
     <row r="349">
       <c r="A349" t="n">
-        <v>19.59</v>
+        <v>19.24</v>
       </c>
       <c r="B349" t="n">
         <v>0.07262</v>
-      </c>
-      <c r="C349" t="n">
-        <v>0.26958</v>
       </c>
       <c r="D349" t="n">
         <v>0.05</v>
@@ -14499,13 +14499,10 @@
     </row>
     <row r="350">
       <c r="A350" t="n">
-        <v>19.7</v>
+        <v>19.36</v>
       </c>
       <c r="B350" t="n">
         <v>0.07262</v>
-      </c>
-      <c r="C350" t="n">
-        <v>0.26958</v>
       </c>
       <c r="D350" t="n">
         <v>0.05</v>
@@ -14516,10 +14513,13 @@
     </row>
     <row r="351">
       <c r="A351" t="n">
-        <v>19.82</v>
+        <v>19.48</v>
       </c>
       <c r="B351" t="n">
         <v>0.07262</v>
+      </c>
+      <c r="C351" t="n">
+        <v>0.26958</v>
       </c>
       <c r="D351" t="n">
         <v>0.05</v>
@@ -14530,7 +14530,7 @@
     </row>
     <row r="352">
       <c r="A352" t="n">
-        <v>19.94</v>
+        <v>19.58</v>
       </c>
       <c r="B352" t="n">
         <v>0.07262</v>
@@ -14544,7 +14544,7 @@
     </row>
     <row r="353">
       <c r="A353" t="n">
-        <v>20.05</v>
+        <v>19.69</v>
       </c>
       <c r="B353" t="n">
         <v>0.07262</v>
@@ -14558,10 +14558,13 @@
     </row>
     <row r="354">
       <c r="A354" t="n">
-        <v>20.16</v>
+        <v>19.82</v>
       </c>
       <c r="B354" t="n">
         <v>0.07262</v>
+      </c>
+      <c r="C354" t="n">
+        <v>0.26958</v>
       </c>
       <c r="D354" t="n">
         <v>0.05</v>
@@ -14572,13 +14575,10 @@
     </row>
     <row r="355">
       <c r="A355" t="n">
-        <v>20.28</v>
+        <v>19.94</v>
       </c>
       <c r="B355" t="n">
         <v>0.07262</v>
-      </c>
-      <c r="C355" t="n">
-        <v>0.26958</v>
       </c>
       <c r="D355" t="n">
         <v>0.05</v>
@@ -14589,7 +14589,7 @@
     </row>
     <row r="356">
       <c r="A356" t="n">
-        <v>20.39</v>
+        <v>20.05</v>
       </c>
       <c r="B356" t="n">
         <v>0.07262</v>
@@ -14603,7 +14603,7 @@
     </row>
     <row r="357">
       <c r="A357" t="n">
-        <v>20.5</v>
+        <v>20.16</v>
       </c>
       <c r="B357" t="n">
         <v>0.07262</v>
@@ -14617,7 +14617,7 @@
     </row>
     <row r="358">
       <c r="A358" t="n">
-        <v>20.62</v>
+        <v>20.27</v>
       </c>
       <c r="B358" t="n">
         <v>0.07262</v>
@@ -14631,7 +14631,7 @@
     </row>
     <row r="359">
       <c r="A359" t="n">
-        <v>20.73</v>
+        <v>20.38</v>
       </c>
       <c r="B359" t="n">
         <v>0.07262</v>
@@ -14645,7 +14645,7 @@
     </row>
     <row r="360">
       <c r="A360" t="n">
-        <v>20.83</v>
+        <v>20.49</v>
       </c>
       <c r="B360" t="n">
         <v>0.07262</v>
@@ -14659,7 +14659,7 @@
     </row>
     <row r="361">
       <c r="A361" t="n">
-        <v>20.95</v>
+        <v>20.6</v>
       </c>
       <c r="B361" t="n">
         <v>0.07262</v>
@@ -14673,10 +14673,13 @@
     </row>
     <row r="362">
       <c r="A362" t="n">
-        <v>21.06</v>
+        <v>20.72</v>
       </c>
       <c r="B362" t="n">
         <v>0.07262</v>
+      </c>
+      <c r="C362" t="n">
+        <v>0.26958</v>
       </c>
       <c r="D362" t="n">
         <v>0.05</v>
@@ -14687,7 +14690,7 @@
     </row>
     <row r="363">
       <c r="A363" t="n">
-        <v>21.16</v>
+        <v>20.83</v>
       </c>
       <c r="B363" t="n">
         <v>0.07262</v>
@@ -14701,7 +14704,7 @@
     </row>
     <row r="364">
       <c r="A364" t="n">
-        <v>21.28</v>
+        <v>20.95</v>
       </c>
       <c r="B364" t="n">
         <v>0.07262</v>
@@ -14715,13 +14718,10 @@
     </row>
     <row r="365">
       <c r="A365" t="n">
-        <v>21.39</v>
+        <v>21.08</v>
       </c>
       <c r="B365" t="n">
         <v>0.07262</v>
-      </c>
-      <c r="C365" t="n">
-        <v>0.26958</v>
       </c>
       <c r="D365" t="n">
         <v>0.05</v>
@@ -14732,7 +14732,7 @@
     </row>
     <row r="366">
       <c r="A366" t="n">
-        <v>21.52</v>
+        <v>21.19</v>
       </c>
       <c r="B366" t="n">
         <v>0.07262</v>
@@ -14746,7 +14746,7 @@
     </row>
     <row r="367">
       <c r="A367" t="n">
-        <v>21.63</v>
+        <v>21.3</v>
       </c>
       <c r="B367" t="n">
         <v>0.07262</v>
@@ -14760,7 +14760,7 @@
     </row>
     <row r="368">
       <c r="A368" t="n">
-        <v>21.76</v>
+        <v>21.42</v>
       </c>
       <c r="B368" t="n">
         <v>0.07262</v>
@@ -14774,7 +14774,7 @@
     </row>
     <row r="369">
       <c r="A369" t="n">
-        <v>21.87</v>
+        <v>21.53</v>
       </c>
       <c r="B369" t="n">
         <v>0.07262</v>
@@ -14788,7 +14788,7 @@
     </row>
     <row r="370">
       <c r="A370" t="n">
-        <v>21.99</v>
+        <v>21.65</v>
       </c>
       <c r="B370" t="n">
         <v>0.07262</v>
@@ -14802,7 +14802,7 @@
     </row>
     <row r="371">
       <c r="A371" t="n">
-        <v>22.12</v>
+        <v>21.76</v>
       </c>
       <c r="B371" t="n">
         <v>0.07262</v>
@@ -14816,7 +14816,7 @@
     </row>
     <row r="372">
       <c r="A372" t="n">
-        <v>22.24</v>
+        <v>21.87</v>
       </c>
       <c r="B372" t="n">
         <v>0.07262</v>
@@ -14830,7 +14830,7 @@
     </row>
     <row r="373">
       <c r="A373" t="n">
-        <v>22.35</v>
+        <v>21.98</v>
       </c>
       <c r="B373" t="n">
         <v>0.07262</v>
@@ -14844,13 +14844,10 @@
     </row>
     <row r="374">
       <c r="A374" t="n">
-        <v>22.48</v>
+        <v>22.1</v>
       </c>
       <c r="B374" t="n">
         <v>0.07262</v>
-      </c>
-      <c r="C374" t="n">
-        <v>0.26958</v>
       </c>
       <c r="D374" t="n">
         <v>0.05</v>
@@ -14861,7 +14858,7 @@
     </row>
     <row r="375">
       <c r="A375" t="n">
-        <v>22.59</v>
+        <v>22.21</v>
       </c>
       <c r="B375" t="n">
         <v>0.07262</v>
@@ -14875,7 +14872,7 @@
     </row>
     <row r="376">
       <c r="A376" t="n">
-        <v>22.73</v>
+        <v>22.33</v>
       </c>
       <c r="B376" t="n">
         <v>0.07262</v>
@@ -14889,10 +14886,13 @@
     </row>
     <row r="377">
       <c r="A377" t="n">
-        <v>22.85</v>
+        <v>22.44</v>
       </c>
       <c r="B377" t="n">
         <v>0.07262</v>
+      </c>
+      <c r="C377" t="n">
+        <v>0.26958</v>
       </c>
       <c r="D377" t="n">
         <v>0.05</v>
@@ -14903,10 +14903,13 @@
     </row>
     <row r="378">
       <c r="A378" t="n">
-        <v>22.97</v>
+        <v>22.55</v>
       </c>
       <c r="B378" t="n">
         <v>0.07262</v>
+      </c>
+      <c r="C378" t="n">
+        <v>0.26958</v>
       </c>
       <c r="D378" t="n">
         <v>0.05</v>
@@ -14917,13 +14920,10 @@
     </row>
     <row r="379">
       <c r="A379" t="n">
-        <v>23.11</v>
+        <v>22.66</v>
       </c>
       <c r="B379" t="n">
         <v>0.07262</v>
-      </c>
-      <c r="C379" t="n">
-        <v>0.26958</v>
       </c>
       <c r="D379" t="n">
         <v>0.05</v>
@@ -14934,10 +14934,13 @@
     </row>
     <row r="380">
       <c r="A380" t="n">
-        <v>23.27</v>
+        <v>22.76</v>
       </c>
       <c r="B380" t="n">
         <v>0.07262</v>
+      </c>
+      <c r="C380" t="n">
+        <v>0.26958</v>
       </c>
       <c r="D380" t="n">
         <v>0.05</v>
@@ -14948,7 +14951,7 @@
     </row>
     <row r="381">
       <c r="A381" t="n">
-        <v>23.37</v>
+        <v>22.88</v>
       </c>
       <c r="B381" t="n">
         <v>0.07262</v>
@@ -14962,7 +14965,7 @@
     </row>
     <row r="382">
       <c r="A382" t="n">
-        <v>23.48</v>
+        <v>23.01</v>
       </c>
       <c r="B382" t="n">
         <v>0.07262</v>
@@ -14976,7 +14979,7 @@
     </row>
     <row r="383">
       <c r="A383" t="n">
-        <v>23.61</v>
+        <v>23.12</v>
       </c>
       <c r="B383" t="n">
         <v>0.07262</v>
@@ -14990,13 +14993,10 @@
     </row>
     <row r="384">
       <c r="A384" t="n">
-        <v>23.73</v>
+        <v>23.24</v>
       </c>
       <c r="B384" t="n">
         <v>0.07262</v>
-      </c>
-      <c r="C384" t="n">
-        <v>0.26958</v>
       </c>
       <c r="D384" t="n">
         <v>0.05</v>
@@ -15007,13 +15007,10 @@
     </row>
     <row r="385">
       <c r="A385" t="n">
-        <v>23.84</v>
+        <v>23.35</v>
       </c>
       <c r="B385" t="n">
         <v>0.07262</v>
-      </c>
-      <c r="C385" t="n">
-        <v>0.26958</v>
       </c>
       <c r="D385" t="n">
         <v>0.05</v>
@@ -15024,10 +15021,13 @@
     </row>
     <row r="386">
       <c r="A386" t="n">
-        <v>23.96</v>
+        <v>23.47</v>
       </c>
       <c r="B386" t="n">
         <v>0.07262</v>
+      </c>
+      <c r="C386" t="n">
+        <v>0.26958</v>
       </c>
       <c r="D386" t="n">
         <v>0.05</v>
@@ -15038,7 +15038,7 @@
     </row>
     <row r="387">
       <c r="A387" t="n">
-        <v>24.08</v>
+        <v>23.58</v>
       </c>
       <c r="B387" t="n">
         <v>0.07262</v>
@@ -15052,7 +15052,7 @@
     </row>
     <row r="388">
       <c r="A388" t="n">
-        <v>24.19</v>
+        <v>23.69</v>
       </c>
       <c r="B388" t="n">
         <v>0.07262</v>
@@ -15066,7 +15066,7 @@
     </row>
     <row r="389">
       <c r="A389" t="n">
-        <v>24.31</v>
+        <v>23.81</v>
       </c>
       <c r="B389" t="n">
         <v>0.07262</v>
@@ -15080,7 +15080,7 @@
     </row>
     <row r="390">
       <c r="A390" t="n">
-        <v>24.42</v>
+        <v>23.93</v>
       </c>
       <c r="B390" t="n">
         <v>0.07262</v>
@@ -15094,7 +15094,7 @@
     </row>
     <row r="391">
       <c r="A391" t="n">
-        <v>24.53</v>
+        <v>24.03</v>
       </c>
       <c r="B391" t="n">
         <v>0.07262</v>
@@ -15108,7 +15108,7 @@
     </row>
     <row r="392">
       <c r="A392" t="n">
-        <v>24.66</v>
+        <v>24.14</v>
       </c>
       <c r="B392" t="n">
         <v>0.07262</v>
@@ -15122,7 +15122,7 @@
     </row>
     <row r="393">
       <c r="A393" t="n">
-        <v>24.77</v>
+        <v>24.24</v>
       </c>
       <c r="B393" t="n">
         <v>0.07262</v>
@@ -15139,7 +15139,7 @@
     </row>
     <row r="394">
       <c r="A394" t="n">
-        <v>24.88</v>
+        <v>24.36</v>
       </c>
       <c r="B394" t="n">
         <v>0.07262</v>
@@ -15148,6 +15148,79 @@
         <v>0.05</v>
       </c>
       <c r="E394" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="n">
+        <v>24.48</v>
+      </c>
+      <c r="B395" t="n">
+        <v>0.07262</v>
+      </c>
+      <c r="D395" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E395" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="B396" t="n">
+        <v>0.07262</v>
+      </c>
+      <c r="D396" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E396" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="B397" t="n">
+        <v>0.07262</v>
+      </c>
+      <c r="C397" t="n">
+        <v>0.26958</v>
+      </c>
+      <c r="D397" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E397" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="n">
+        <v>24.81</v>
+      </c>
+      <c r="B398" t="n">
+        <v>0.07262</v>
+      </c>
+      <c r="D398" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E398" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="n">
+        <v>24.92</v>
+      </c>
+      <c r="B399" t="n">
+        <v>0.07262</v>
+      </c>
+      <c r="D399" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E399" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -15418,7 +15491,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>556aa6c515e58169</t>
+          <t>8f1af0be7fa49d74</t>
         </is>
       </c>
     </row>
@@ -15452,7 +15525,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>6c38a06cdc712700</t>
+          <t>b9adb4b8a2b4c7cc</t>
         </is>
       </c>
     </row>
@@ -15571,7 +15644,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>09b64411a0aa6eee</t>
+          <t>0c7524ce74150076</t>
         </is>
       </c>
     </row>
@@ -15588,7 +15661,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>5fcba17c82f6274d</t>
+          <t>8a73bc7b461565b9</t>
         </is>
       </c>
     </row>
@@ -15605,7 +15678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ffaa16eb1b7b4e3c</t>
+          <t>be8476ed7628b493</t>
         </is>
       </c>
     </row>
